--- a/results/block3_results/label/Normal_2/branches/dataframes/dataset_LCA_B07_Normal_2.xlsx
+++ b/results/block3_results/label/Normal_2/branches/dataframes/dataset_LCA_B07_Normal_2.xlsx
@@ -553,14 +553,14 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>16.47241871755802</v>
+        <v>17.97859383075771</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="b">
@@ -606,14 +606,14 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
       <c r="L3" t="n">
         <v>0.3601154259422569</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>17.13662195006867</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="b">
@@ -659,14 +659,14 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
       <c r="L4" t="n">
         <v>0.4856598649306226</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>17.13662195006867</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="b">
@@ -712,14 +712,14 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
       <c r="L5" t="n">
         <v>0.9997363939876458</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>17.726221843046</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="b">
@@ -765,14 +765,14 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
       <c r="L6" t="n">
         <v>1.0424394394317</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>17.726221843046</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="b">
@@ -818,14 +818,14 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
       <c r="L7" t="n">
         <v>1.396593121187507</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>17.91045501285387</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="b">
@@ -871,14 +871,14 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
       <c r="L8" t="n">
         <v>1.462131922311446</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>17.91045501285387</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="b">
@@ -924,14 +924,14 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
       <c r="L9" t="n">
         <v>1.985418126971284</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>18.31313623191253</v>
+        <v>18.62276903281257</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="b">
@@ -977,14 +977,14 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
       <c r="L10" t="n">
         <v>2.065633939901772</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>18.31313623191253</v>
+        <v>19.36546901145579</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="b">
@@ -1030,14 +1030,14 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
       <c r="L11" t="n">
         <v>2.078774461852574</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>18.31313623191253</v>
+        <v>19.36546901145579</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="b">
@@ -1083,14 +1083,14 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
       <c r="L12" t="n">
         <v>2.407095228836781</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>18.19251281614148</v>
+        <v>21.00429376107303</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="b">
@@ -1136,14 +1136,14 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
       <c r="L13" t="n">
         <v>2.41287629650813</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>18.19251281614148</v>
+        <v>21.00429376107303</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="b">
@@ -1189,14 +1189,14 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
       <c r="L14" t="n">
         <v>2.481604987745707</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>18.19251281614148</v>
+        <v>21.00429376107303</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="b">
@@ -1242,14 +1242,14 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
       <c r="L15" t="n">
         <v>2.728679744521261</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>18.32725138968634</v>
+        <v>21.19153026999809</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="b">
@@ -1295,14 +1295,14 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
       <c r="L16" t="n">
         <v>2.898721431260564</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>18.43101520147438</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="b">
@@ -1348,14 +1348,14 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
       <c r="L17" t="n">
         <v>3.338905849183162</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>18.7683839298948</v>
+        <v>0.6098121915157551</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="b">
@@ -1401,14 +1401,14 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
       <c r="L18" t="n">
         <v>3.973653740040507</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>18.0508829171354</v>
+        <v>0.8260418668445116</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="b">
@@ -1454,14 +1454,14 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
       <c r="L19" t="n">
         <v>4.026888936942744</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>17.99032586218531</v>
+        <v>0.8260418668445116</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="b">
@@ -1507,14 +1507,14 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
       <c r="L20" t="n">
         <v>4.69477999770448</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>17.81814662802715</v>
+        <v>33.47802446979679</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="b">
@@ -1560,14 +1560,14 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
       <c r="L21" t="n">
         <v>4.709762932052915</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>17.81814662802715</v>
+        <v>33.47802446979679</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="b">
@@ -1613,14 +1613,14 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
       <c r="L22" t="n">
         <v>4.833297950717468</v>
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>17.81814662802715</v>
+        <v>23.49332569301106</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="b">
@@ -1666,26 +1666,20 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="L23" t="n">
         <v>5.15606352961821</v>
       </c>
-      <c r="M23" t="n">
-        <v>0.1865502853357017</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>18.06393349092241</v>
-      </c>
-      <c r="O23" t="n">
-        <v>9.125241888129054</v>
-      </c>
+        <v>24.43540424109552</v>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-80.51487203848096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1725,26 +1719,20 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="L24" t="n">
         <v>5.157856096412854</v>
       </c>
-      <c r="M24" t="n">
-        <v>0.1865502853357017</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>18.06393349092241</v>
-      </c>
-      <c r="O24" t="n">
-        <v>9.125241888129054</v>
-      </c>
+        <v>24.43540424109552</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-80.51487203848096</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1784,26 +1772,20 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
       <c r="L25" t="n">
         <v>5.202839099736595</v>
       </c>
-      <c r="M25" t="n">
-        <v>0.9027069616915873</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>18.06393349092241</v>
-      </c>
-      <c r="O25" t="n">
-        <v>9.483320226306997</v>
-      </c>
+        <v>22.3884218643085</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-75.90096843115819</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1843,26 +1825,20 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
       <c r="L26" t="n">
         <v>5.384423328866162</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.9027069616915873</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>18.25587384616591</v>
-      </c>
-      <c r="O26" t="n">
-        <v>9.579290403928749</v>
-      </c>
+        <v>22.3884218643085</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-78.89239419070582</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1902,26 +1878,20 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
       <c r="L27" t="n">
         <v>5.794205644713168</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.45343381859624</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>18.25615665036968</v>
-      </c>
-      <c r="O27" t="n">
-        <v>10.85479523448296</v>
-      </c>
+        <v>22.19039193738289</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-62.6602548148024</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1961,26 +1931,20 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
       <c r="L28" t="n">
         <v>5.98953720609348</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.45343381859624</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>18.32865305918012</v>
-      </c>
-      <c r="O28" t="n">
-        <v>10.89104343888818</v>
-      </c>
+        <v>21.65492269454226</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-62.7596285196306</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2020,26 +1984,20 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
       <c r="L29" t="n">
         <v>6.195379574156589</v>
       </c>
-      <c r="M29" t="n">
-        <v>3.45343381859624</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>18.32865305918012</v>
-      </c>
-      <c r="O29" t="n">
-        <v>10.89104343888818</v>
-      </c>
+        <v>20.57281945073719</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-63.61486597035402</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2079,26 +2037,20 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
       <c r="L30" t="n">
         <v>6.269644802794724</v>
       </c>
-      <c r="M30" t="n">
-        <v>5.333486823954726</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>18.32865305918012</v>
-      </c>
-      <c r="O30" t="n">
-        <v>11.83106994156742</v>
-      </c>
+        <v>20.50179656936968</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>-50.7107862203902</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2138,26 +2090,20 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
       <c r="L31" t="n">
         <v>6.308240156541436</v>
       </c>
-      <c r="M31" t="n">
-        <v>5.333486823954726</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>18.32865305918012</v>
-      </c>
-      <c r="O31" t="n">
-        <v>11.83106994156742</v>
-      </c>
+        <v>20.1367742844572</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>-51.38491363259601</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2197,26 +2143,20 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
       <c r="L32" t="n">
         <v>6.632326531712934</v>
       </c>
-      <c r="M32" t="n">
-        <v>6.042760034830393</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>18.22115293721825</v>
-      </c>
-      <c r="O32" t="n">
-        <v>12.13195648602432</v>
-      </c>
+        <v>10.05556289128236</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-49.28142897164503</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2256,26 +2196,20 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
       <c r="L33" t="n">
         <v>6.704713422911015</v>
       </c>
-      <c r="M33" t="n">
-        <v>6.042760034830393</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>18.22115293721825</v>
-      </c>
-      <c r="O33" t="n">
-        <v>12.13195648602432</v>
-      </c>
+        <v>9.249788548710319</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-49.6859951795648</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2315,26 +2249,20 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
       <c r="L34" t="n">
         <v>6.730332276537041</v>
       </c>
-      <c r="M34" t="n">
-        <v>9.774211633003286</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>18.22115293721825</v>
-      </c>
-      <c r="O34" t="n">
-        <v>13.99768228511077</v>
-      </c>
+        <v>9.249788548710319</v>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-29.7346191388681</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2374,26 +2302,20 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
       <c r="L35" t="n">
         <v>6.828344639645609</v>
       </c>
-      <c r="M35" t="n">
-        <v>9.774211633003286</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>18.33354581660341</v>
-      </c>
-      <c r="O35" t="n">
-        <v>14.05387872480335</v>
-      </c>
+        <v>9.001199936508684</v>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>-29.88111493776982</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2433,26 +2355,20 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
       <c r="L36" t="n">
         <v>7.105887599515331</v>
       </c>
-      <c r="M36" t="n">
-        <v>10.50943319366649</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>19.21730918670944</v>
-      </c>
-      <c r="O36" t="n">
-        <v>14.86337119018796</v>
-      </c>
+        <v>9.001199936508684</v>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-23.20984248850575</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2492,26 +2408,20 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
       <c r="L37" t="n">
         <v>7.505383074245886</v>
       </c>
-      <c r="M37" t="n">
-        <v>12.33737930054762</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>21.13985137760104</v>
-      </c>
-      <c r="O37" t="n">
-        <v>16.73861533907433</v>
-      </c>
+        <v>8.859202453554882</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>-8.685888573311029</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2551,26 +2461,20 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
       <c r="L38" t="n">
         <v>7.795590577622448</v>
       </c>
-      <c r="M38" t="n">
-        <v>1.112358201660258</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>21.24478764721551</v>
-      </c>
-      <c r="O38" t="n">
-        <v>11.17857292443788</v>
-      </c>
+        <v>8.988563827679902</v>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>-63.94983074825649</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2610,26 +2514,20 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
       <c r="L39" t="n">
         <v>7.800308209273576</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.112358201660258</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>21.24478764721551</v>
-      </c>
-      <c r="O39" t="n">
-        <v>11.17857292443788</v>
-      </c>
+        <v>8.988563827679902</v>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>-63.94983074825649</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2669,26 +2567,20 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
       <c r="L40" t="n">
         <v>7.809582355781412</v>
       </c>
-      <c r="M40" t="n">
-        <v>1.112358201660258</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>21.24478764721551</v>
-      </c>
-      <c r="O40" t="n">
-        <v>11.17857292443788</v>
-      </c>
+        <v>8.988563827679902</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>-64.87806919594961</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2728,26 +2620,20 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
       <c r="L41" t="n">
         <v>8.010742044589922</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.062777698332418</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>21.24478764721551</v>
-      </c>
-      <c r="O41" t="n">
-        <v>11.15378267277396</v>
-      </c>
+        <v>9.057072937995757</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>-66.47800841328528</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2787,26 +2673,20 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
       <c r="L42" t="n">
         <v>8.064536515356497</v>
       </c>
-      <c r="M42" t="n">
-        <v>1.062777698332418</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>21.24478764721551</v>
-      </c>
-      <c r="O42" t="n">
-        <v>11.15378267277396</v>
-      </c>
+        <v>9.045523308623421</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>-66.5809883227012</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2846,26 +2726,20 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
       <c r="L43" t="n">
         <v>8.245257882661589</v>
       </c>
-      <c r="M43" t="n">
-        <v>0.5772589909199825</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
-        <v>20.91401769073484</v>
-      </c>
-      <c r="O43" t="n">
-        <v>10.74563834082741</v>
-      </c>
+        <v>8.809891251011997</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>-75.32283907337585</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2905,26 +2779,20 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
       <c r="L44" t="n">
         <v>8.36033404621746</v>
       </c>
-      <c r="M44" t="n">
-        <v>0.5772589909199825</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>20.91401769073484</v>
-      </c>
-      <c r="O44" t="n">
-        <v>10.74563834082741</v>
-      </c>
+        <v>8.01349959414503</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>-74.66048395268845</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2964,26 +2832,20 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
       <c r="L45" t="n">
         <v>8.379490580809469</v>
       </c>
-      <c r="M45" t="n">
-        <v>0.5772589909199825</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>20.91401769073484</v>
-      </c>
-      <c r="O45" t="n">
-        <v>10.74563834082741</v>
-      </c>
+        <v>8.01349959414503</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>-74.37556371948281</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3023,26 +2885,20 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
       <c r="L46" t="n">
         <v>8.444966427389842</v>
       </c>
-      <c r="M46" t="n">
-        <v>0.5772589909199825</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>20.91401769073484</v>
-      </c>
-      <c r="O46" t="n">
-        <v>10.74563834082741</v>
-      </c>
+        <v>8.01349959414503</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>-72.60426882346327</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3082,26 +2938,20 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
       <c r="L47" t="n">
         <v>8.689563461638169</v>
       </c>
-      <c r="M47" t="n">
-        <v>15.92122532206255</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>18.31538578099143</v>
-      </c>
-      <c r="O47" t="n">
-        <v>17.11830555152699</v>
-      </c>
+        <v>7.613353376700388</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>-6.04161722095522</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3141,26 +2991,20 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
       <c r="L48" t="n">
         <v>8.814229518264719</v>
       </c>
-      <c r="M48" t="n">
-        <v>15.92122532206255</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>18.31538578099143</v>
-      </c>
-      <c r="O48" t="n">
-        <v>17.11830555152699</v>
-      </c>
+        <v>7.613353376700388</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>-5.618151665867632</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3200,26 +3044,20 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
       <c r="L49" t="n">
         <v>8.945459226006554</v>
       </c>
-      <c r="M49" t="n">
-        <v>15.92122532206255</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>41.15307330033042</v>
-      </c>
-      <c r="O49" t="n">
-        <v>28.53714931119648</v>
-      </c>
+        <v>7.52583147660655</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>36.74601930174862</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3259,26 +3097,20 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
       <c r="L50" t="n">
         <v>9.083281619530522</v>
       </c>
-      <c r="M50" t="n">
-        <v>15.92244207042752</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>55.6368087571851</v>
-      </c>
-      <c r="O50" t="n">
-        <v>35.77962541380631</v>
-      </c>
+        <v>7.649937527108574</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>49.71907711687957</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3318,26 +3150,20 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
       <c r="L51" t="n">
         <v>9.094523868272876</v>
       </c>
-      <c r="M51" t="n">
-        <v>15.92244207042752</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>55.6368087571851</v>
-      </c>
-      <c r="O51" t="n">
-        <v>35.77962541380631</v>
-      </c>
+        <v>7.649937527108574</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>49.71907711687957</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3377,26 +3203,20 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
       <c r="L52" t="n">
         <v>9.571436529592708</v>
       </c>
-      <c r="M52" t="n">
-        <v>15.90440478338968</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
-        <v>33.49840842426605</v>
-      </c>
-      <c r="O52" t="n">
-        <v>24.70140660382786</v>
-      </c>
+        <v>7.878513743038085</v>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>28.14546586736805</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3436,26 +3256,20 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
       <c r="L53" t="n">
         <v>9.588798518960147</v>
       </c>
-      <c r="M53" t="n">
-        <v>15.90440478338968</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
-        <v>33.49840842426605</v>
-      </c>
-      <c r="O53" t="n">
-        <v>24.70140660382786</v>
-      </c>
+        <v>7.878513743038085</v>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>28.1429698653133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3495,26 +3309,20 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
       <c r="L54" t="n">
         <v>9.588861432559142</v>
       </c>
-      <c r="M54" t="n">
-        <v>15.90440478338968</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
-        <v>33.49840842426605</v>
-      </c>
-      <c r="O54" t="n">
-        <v>24.70140660382786</v>
-      </c>
+        <v>7.878513743038085</v>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>28.1429698653133</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3554,26 +3362,20 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
       <c r="L55" t="n">
         <v>9.738802677756482</v>
       </c>
-      <c r="M55" t="n">
-        <v>15.90440478338968</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
-        <v>23.51115280153341</v>
-      </c>
-      <c r="O55" t="n">
-        <v>19.70777879246154</v>
-      </c>
+        <v>7.996384831667157</v>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>9.588255400741552</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3613,25 +3415,25 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
       <c r="L56" t="n">
         <v>10.00250162688671</v>
       </c>
       <c r="M56" t="n">
-        <v>16.47241871755802</v>
+        <v>0.1865600545781031</v>
       </c>
       <c r="N56" t="n">
-        <v>23.07759859367414</v>
+        <v>8.026924327986121</v>
       </c>
       <c r="O56" t="n">
-        <v>19.77500865561608</v>
+        <v>4.106742191282112</v>
       </c>
       <c r="P56" t="b">
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>9.01518668068395</v>
+        <v>-337.7823830510491</v>
       </c>
     </row>
     <row r="57">
@@ -3672,25 +3474,25 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
       <c r="L57" t="n">
         <v>10.05381141463611</v>
       </c>
       <c r="M57" t="n">
-        <v>16.47241871755802</v>
+        <v>0.1865600545781031</v>
       </c>
       <c r="N57" t="n">
-        <v>23.03288491493475</v>
+        <v>8.026924327986121</v>
       </c>
       <c r="O57" t="n">
-        <v>19.75265181624638</v>
+        <v>4.106742191282112</v>
       </c>
       <c r="P57" t="b">
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>8.626725456679186</v>
+        <v>-339.3286023736751</v>
       </c>
     </row>
     <row r="58">
@@ -3731,25 +3533,25 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
       <c r="L58" t="n">
         <v>10.08551207038884</v>
       </c>
       <c r="M58" t="n">
-        <v>16.47241871755802</v>
+        <v>0.1865600545781031</v>
       </c>
       <c r="N58" t="n">
-        <v>22.66480968815676</v>
+        <v>8.026924327986121</v>
       </c>
       <c r="O58" t="n">
-        <v>19.56861420285739</v>
+        <v>4.106742191282112</v>
       </c>
       <c r="P58" t="b">
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>7.689255336820288</v>
+        <v>-339.6632681978548</v>
       </c>
     </row>
     <row r="59">
@@ -3790,25 +3592,25 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="L59" t="n">
         <v>10.5202175832988</v>
       </c>
       <c r="M59" t="n">
-        <v>17.13662195006867</v>
+        <v>1.329840539349983</v>
       </c>
       <c r="N59" t="n">
-        <v>22.4810658565194</v>
+        <v>8.338770570052079</v>
       </c>
       <c r="O59" t="n">
-        <v>19.80884390329404</v>
+        <v>4.834305554701031</v>
       </c>
       <c r="P59" t="b">
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>7.839781386080203</v>
+        <v>-277.6214803062911</v>
       </c>
     </row>
     <row r="60">
@@ -3849,25 +3651,25 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="L60" t="n">
         <v>10.52704179843524</v>
       </c>
       <c r="M60" t="n">
-        <v>17.13662195006867</v>
+        <v>1.329840539349983</v>
       </c>
       <c r="N60" t="n">
-        <v>22.4810658565194</v>
+        <v>8.338770570052079</v>
       </c>
       <c r="O60" t="n">
-        <v>19.80884390329404</v>
+        <v>4.834305554701031</v>
       </c>
       <c r="P60" t="b">
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>7.839781386080203</v>
+        <v>-277.6214803062911</v>
       </c>
     </row>
     <row r="61">
@@ -3908,25 +3710,25 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
       <c r="L61" t="n">
         <v>10.54346045399975</v>
       </c>
       <c r="M61" t="n">
-        <v>17.13662195006867</v>
+        <v>1.329840539349983</v>
       </c>
       <c r="N61" t="n">
-        <v>22.4810658565194</v>
+        <v>8.338770570052079</v>
       </c>
       <c r="O61" t="n">
-        <v>19.80884390329404</v>
+        <v>4.834305554701031</v>
       </c>
       <c r="P61" t="b">
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>7.790987491843671</v>
+        <v>-277.8279237633931</v>
       </c>
     </row>
     <row r="62">
@@ -3967,25 +3769,25 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
       <c r="L62" t="n">
         <v>10.81814752693169</v>
       </c>
       <c r="M62" t="n">
-        <v>17.65643758803501</v>
+        <v>3.466416537272089</v>
       </c>
       <c r="N62" t="n">
-        <v>22.41499665150971</v>
+        <v>8.661114516403142</v>
       </c>
       <c r="O62" t="n">
-        <v>20.03571711977236</v>
+        <v>6.063765526837615</v>
       </c>
       <c r="P62" t="b">
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>8.881940480415906</v>
+        <v>-201.0577678132537</v>
       </c>
     </row>
     <row r="63">
@@ -4026,25 +3828,25 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="L63" t="n">
         <v>10.97434831349831</v>
       </c>
       <c r="M63" t="n">
-        <v>17.726221843046</v>
+        <v>3.466416537272089</v>
       </c>
       <c r="N63" t="n">
-        <v>25.95407996901959</v>
+        <v>8.957982002673143</v>
       </c>
       <c r="O63" t="n">
-        <v>21.84015090603279</v>
+        <v>6.212199269972616</v>
       </c>
       <c r="P63" t="b">
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>16.07817575052888</v>
+        <v>-195.3998104532507</v>
       </c>
     </row>
     <row r="64">
@@ -4085,25 +3887,25 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="L64" t="n">
         <v>11.74633329171321</v>
       </c>
       <c r="M64" t="n">
-        <v>18.15983980085726</v>
+        <v>9.635797748144768</v>
       </c>
       <c r="N64" t="n">
-        <v>9.313454523502497</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="O64" t="n">
-        <v>13.73664716217988</v>
+        <v>9.651439132700208</v>
       </c>
       <c r="P64" t="b">
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>-32.64629077308787</v>
+        <v>-89.79992697155619</v>
       </c>
     </row>
     <row r="65">
@@ -4144,25 +3946,25 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.30135144683257</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="L65" t="n">
         <v>11.77214382546127</v>
       </c>
       <c r="M65" t="n">
-        <v>18.15983980085726</v>
+        <v>9.635797748144768</v>
       </c>
       <c r="N65" t="n">
-        <v>9.313454523502497</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="O65" t="n">
-        <v>13.73664716217988</v>
+        <v>9.651439132700208</v>
       </c>
       <c r="P65" t="b">
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>-33.23011962642792</v>
+        <v>-89.79992697155619</v>
       </c>
     </row>
     <row r="66">
@@ -4203,25 +4005,25 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
       <c r="L66" t="n">
         <v>11.81300090790428</v>
       </c>
       <c r="M66" t="n">
-        <v>18.25333437977661</v>
+        <v>9.635797748144768</v>
       </c>
       <c r="N66" t="n">
-        <v>9.006605764587595</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="O66" t="n">
-        <v>13.6299700721821</v>
+        <v>9.651439132700208</v>
       </c>
       <c r="P66" t="b">
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>-34.5090687617943</v>
+        <v>-90.16140504183177</v>
       </c>
     </row>
     <row r="67">
@@ -4262,25 +4064,25 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>18.56867116826499</v>
+        <v>18.62276903281257</v>
       </c>
       <c r="L67" t="n">
         <v>11.9288914108339</v>
       </c>
       <c r="M67" t="n">
-        <v>18.25333437977661</v>
+        <v>9.635797748144768</v>
       </c>
       <c r="N67" t="n">
-        <v>9.006605764587595</v>
+        <v>9.748095555311115</v>
       </c>
       <c r="O67" t="n">
-        <v>13.6299700721821</v>
+        <v>9.691946651727942</v>
       </c>
       <c r="P67" t="b">
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>-36.2341301552999</v>
+        <v>-92.14683800898121</v>
       </c>
     </row>
     <row r="68">
@@ -4321,25 +4123,25 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.21730918670944</v>
+        <v>19.36546901145579</v>
       </c>
       <c r="L68" t="n">
         <v>12.08891459706511</v>
       </c>
       <c r="M68" t="n">
-        <v>18.31313623191253</v>
+        <v>10.50475136658863</v>
       </c>
       <c r="N68" t="n">
-        <v>9.006605764587595</v>
+        <v>9.748095555311115</v>
       </c>
       <c r="O68" t="n">
-        <v>13.65987099825006</v>
+        <v>10.12642346094987</v>
       </c>
       <c r="P68" t="b">
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>-40.68441194775063</v>
+        <v>-91.23700570230034</v>
       </c>
     </row>
     <row r="69">
@@ -4380,25 +4182,25 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
       <c r="L69" t="n">
         <v>12.20158993547679</v>
       </c>
       <c r="M69" t="n">
-        <v>18.31313623191253</v>
+        <v>10.50475136658863</v>
       </c>
       <c r="N69" t="n">
-        <v>8.855391791179059</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="O69" t="n">
-        <v>13.5842640115458</v>
+        <v>10.21261650910081</v>
       </c>
       <c r="P69" t="b">
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>-46.75350417248745</v>
+        <v>-94.79607763825729</v>
       </c>
     </row>
     <row r="70">
@@ -4439,25 +4241,25 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>19.93538345298557</v>
+        <v>19.89377638396549</v>
       </c>
       <c r="L70" t="n">
         <v>12.20295514949024</v>
       </c>
       <c r="M70" t="n">
-        <v>18.31313623191253</v>
+        <v>10.50475136658863</v>
       </c>
       <c r="N70" t="n">
-        <v>8.855391791179059</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="O70" t="n">
-        <v>13.5842640115458</v>
+        <v>10.21261650910081</v>
       </c>
       <c r="P70" t="b">
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>-46.75350417248745</v>
+        <v>-94.79607763825729</v>
       </c>
     </row>
     <row r="71">
@@ -4498,25 +4300,25 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
       <c r="L71" t="n">
         <v>12.24275482482597</v>
       </c>
       <c r="M71" t="n">
-        <v>18.31313623191253</v>
+        <v>10.50475136658863</v>
       </c>
       <c r="N71" t="n">
-        <v>8.855391791179059</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="O71" t="n">
-        <v>13.5842640115458</v>
+        <v>10.21261650910081</v>
       </c>
       <c r="P71" t="b">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>-47.30143307075922</v>
+        <v>-95.4181094665711</v>
       </c>
     </row>
     <row r="72">
@@ -4557,25 +4359,25 @@
         <v>5</v>
       </c>
       <c r="K72" t="n">
-        <v>20.00981556112236</v>
+        <v>19.95730210915573</v>
       </c>
       <c r="L72" t="n">
         <v>12.24407706735417</v>
       </c>
       <c r="M72" t="n">
-        <v>18.31313623191253</v>
+        <v>11.98254064055079</v>
       </c>
       <c r="N72" t="n">
-        <v>8.855391791179059</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="O72" t="n">
-        <v>13.5842640115458</v>
+        <v>10.95151114608189</v>
       </c>
       <c r="P72" t="b">
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>-47.30143307075922</v>
+        <v>-82.23331778551707</v>
       </c>
     </row>
     <row r="73">
@@ -4616,25 +4418,25 @@
         <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>21.13985137760104</v>
+        <v>21.00429376107303</v>
       </c>
       <c r="L73" t="n">
         <v>12.50480286071748</v>
       </c>
       <c r="M73" t="n">
-        <v>18.19251281614148</v>
+        <v>12.33786735892068</v>
       </c>
       <c r="N73" t="n">
-        <v>8.855391791179059</v>
+        <v>10.03384085376461</v>
       </c>
       <c r="O73" t="n">
-        <v>13.52395230366027</v>
+        <v>11.18585410634264</v>
       </c>
       <c r="P73" t="b">
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>-56.31415212755167</v>
+        <v>-87.77550253550241</v>
       </c>
     </row>
     <row r="74">
@@ -4675,25 +4477,25 @@
         <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>21.25752534241971</v>
+        <v>21.19153026999809</v>
       </c>
       <c r="L74" t="n">
         <v>12.6996605531895</v>
       </c>
       <c r="M74" t="n">
-        <v>18.32725138968634</v>
+        <v>1.112431640076021</v>
       </c>
       <c r="N74" t="n">
-        <v>8.984199379338564</v>
+        <v>10.04873175068141</v>
       </c>
       <c r="O74" t="n">
-        <v>13.65572538451245</v>
+        <v>5.580581695378718</v>
       </c>
       <c r="P74" t="b">
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>-55.66749289297215</v>
+        <v>-279.7369418952652</v>
       </c>
     </row>
     <row r="75">
@@ -4734,25 +4536,25 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="L75" t="n">
         <v>12.83092854483349</v>
       </c>
       <c r="M75" t="n">
-        <v>18.43101520147438</v>
+        <v>1.063099514135826</v>
       </c>
       <c r="N75" t="n">
-        <v>8.984199379338564</v>
+        <v>10.1703113821572</v>
       </c>
       <c r="O75" t="n">
-        <v>13.70760729040647</v>
+        <v>5.616705448146514</v>
       </c>
       <c r="P75" t="b">
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>-54.98538291277193</v>
+        <v>-277.4938050626382</v>
       </c>
     </row>
     <row r="76">
@@ -4793,25 +4595,25 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>21.24478764721551</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="L76" t="n">
         <v>12.83339386654114</v>
       </c>
       <c r="M76" t="n">
-        <v>18.43101520147438</v>
+        <v>1.063099514135826</v>
       </c>
       <c r="N76" t="n">
-        <v>8.984199379338564</v>
+        <v>10.1703113821572</v>
       </c>
       <c r="O76" t="n">
-        <v>13.70760729040647</v>
+        <v>5.616705448146514</v>
       </c>
       <c r="P76" t="b">
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>-54.98538291277193</v>
+        <v>-277.4938050626382</v>
       </c>
     </row>
     <row r="77">
@@ -4852,25 +4654,25 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>20.91401769073484</v>
+        <v>0.6098121915157551</v>
       </c>
       <c r="L77" t="n">
         <v>13.29885716560498</v>
       </c>
       <c r="M77" t="n">
-        <v>18.83955821569582</v>
+        <v>0.5792498871576799</v>
       </c>
       <c r="N77" t="n">
-        <v>8.817828618037916</v>
+        <v>10.73329757505697</v>
       </c>
       <c r="O77" t="n">
-        <v>13.82869341686687</v>
+        <v>5.656273731107324</v>
       </c>
       <c r="P77" t="b">
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>-51.23639710766889</v>
+        <v>89.21883521722043</v>
       </c>
     </row>
     <row r="78">
@@ -4911,25 +4713,25 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>21.75249733392203</v>
+        <v>22.81637576394737</v>
       </c>
       <c r="L78" t="n">
         <v>13.59256011927195</v>
       </c>
       <c r="M78" t="n">
-        <v>18.15252804766378</v>
+        <v>0.5792498871576799</v>
       </c>
       <c r="N78" t="n">
-        <v>7.881424971903225</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="O78" t="n">
-        <v>13.0169765097835</v>
+        <v>5.70565189892515</v>
       </c>
       <c r="P78" t="b">
         <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>-67.10867779144378</v>
+        <v>-299.8907779187439</v>
       </c>
     </row>
     <row r="79">
@@ -4970,25 +4772,25 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
       <c r="L79" t="n">
         <v>13.61085283169918</v>
       </c>
       <c r="M79" t="n">
-        <v>18.15252804766378</v>
+        <v>0.5792498871576799</v>
       </c>
       <c r="N79" t="n">
-        <v>7.881424971903225</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="O79" t="n">
-        <v>13.0169765097835</v>
+        <v>5.70565189892515</v>
       </c>
       <c r="P79" t="b">
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>-40.70383984503367</v>
+        <v>-293.4947706510699</v>
       </c>
     </row>
     <row r="80">
@@ -5029,25 +4831,25 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>18.31538578099143</v>
+        <v>22.45144185382393</v>
       </c>
       <c r="L80" t="n">
         <v>13.61114564543609</v>
       </c>
       <c r="M80" t="n">
-        <v>18.15252804766378</v>
+        <v>0.5792498871576799</v>
       </c>
       <c r="N80" t="n">
-        <v>7.881424971903225</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="O80" t="n">
-        <v>13.0169765097835</v>
+        <v>5.70565189892515</v>
       </c>
       <c r="P80" t="b">
         <v>1</v>
       </c>
       <c r="Q80" t="n">
-        <v>-40.70383984503367</v>
+        <v>-293.4947706510699</v>
       </c>
     </row>
     <row r="81">
@@ -5088,25 +4890,25 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>41.15307330033042</v>
+        <v>0.8260418668445116</v>
       </c>
       <c r="L81" t="n">
         <v>14.05707472285852</v>
       </c>
       <c r="M81" t="n">
-        <v>17.99032586218531</v>
+        <v>15.9224055805709</v>
       </c>
       <c r="N81" t="n">
-        <v>7.648109426969325</v>
+        <v>11.34493953621662</v>
       </c>
       <c r="O81" t="n">
-        <v>12.81921764457732</v>
+        <v>13.63367255839376</v>
       </c>
       <c r="P81" t="b">
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>-221.0264030249823</v>
+        <v>93.94116395779251</v>
       </c>
     </row>
     <row r="82">
@@ -5147,25 +4949,25 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>55.6368087571851</v>
+        <v>56.23003942877807</v>
       </c>
       <c r="L82" t="n">
         <v>14.07815203372812</v>
       </c>
       <c r="M82" t="n">
-        <v>17.99032586218531</v>
+        <v>15.9224055805709</v>
       </c>
       <c r="N82" t="n">
-        <v>7.648109426969325</v>
+        <v>11.34493953621662</v>
       </c>
       <c r="O82" t="n">
-        <v>12.81921764457732</v>
+        <v>13.63367255839376</v>
       </c>
       <c r="P82" t="b">
         <v>1</v>
       </c>
       <c r="Q82" t="n">
-        <v>-334.0109537083969</v>
+        <v>-312.4350147617361</v>
       </c>
     </row>
     <row r="83">
@@ -5206,25 +5008,25 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
-        <v>42.99916497611289</v>
+        <v>45.66360168374498</v>
       </c>
       <c r="L83" t="n">
         <v>14.39933417279553</v>
       </c>
       <c r="M83" t="n">
-        <v>17.7490806393877</v>
+        <v>15.90529663782263</v>
       </c>
       <c r="N83" t="n">
-        <v>7.833439394377753</v>
+        <v>11.60728634568303</v>
       </c>
       <c r="O83" t="n">
-        <v>12.79126001688272</v>
+        <v>13.75629149175283</v>
       </c>
       <c r="P83" t="b">
         <v>1</v>
       </c>
       <c r="Q83" t="n">
-        <v>-236.1605105310957</v>
+        <v>-231.9470346431756</v>
       </c>
     </row>
     <row r="84">
@@ -5265,25 +5067,25 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
-        <v>40.56424938189363</v>
+        <v>40.59325963239543</v>
       </c>
       <c r="L84" t="n">
         <v>14.47565143150158</v>
       </c>
       <c r="M84" t="n">
-        <v>17.7490806393877</v>
+        <v>15.90529663782263</v>
       </c>
       <c r="N84" t="n">
-        <v>7.877726027147521</v>
+        <v>11.65030216584749</v>
       </c>
       <c r="O84" t="n">
-        <v>12.81340333326761</v>
+        <v>13.77779940183506</v>
       </c>
       <c r="P84" t="b">
         <v>1</v>
       </c>
       <c r="Q84" t="n">
-        <v>-216.5766996234024</v>
+        <v>-194.6280349167286</v>
       </c>
     </row>
     <row r="85">
@@ -5324,25 +5126,25 @@
         <v>6</v>
       </c>
       <c r="K85" t="n">
-        <v>33.49840842426605</v>
+        <v>33.47802446979679</v>
       </c>
       <c r="L85" t="n">
         <v>14.54608857354744</v>
       </c>
       <c r="M85" t="n">
-        <v>17.7490806393877</v>
+        <v>15.90529663782263</v>
       </c>
       <c r="N85" t="n">
-        <v>7.877726027147521</v>
+        <v>11.65030216584749</v>
       </c>
       <c r="O85" t="n">
-        <v>12.81340333326761</v>
+        <v>13.77779940183506</v>
       </c>
       <c r="P85" t="b">
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>-161.4325605227277</v>
+        <v>-142.9852801118432</v>
       </c>
     </row>
     <row r="86">
@@ -5383,25 +5185,25 @@
         <v>6</v>
       </c>
       <c r="K86" t="n">
-        <v>23.51115280153341</v>
+        <v>23.49332569301106</v>
       </c>
       <c r="L86" t="n">
         <v>14.89078715348592</v>
       </c>
       <c r="M86" t="n">
-        <v>17.99225470919088</v>
+        <v>15.94907264007682</v>
       </c>
       <c r="N86" t="n">
-        <v>7.996504394876585</v>
+        <v>12.28927385385947</v>
       </c>
       <c r="O86" t="n">
-        <v>12.99437955203373</v>
+        <v>14.11917324696814</v>
       </c>
       <c r="P86" t="b">
         <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>-80.93324661933326</v>
+        <v>-66.39306907049856</v>
       </c>
     </row>
     <row r="87">
@@ -5442,25 +5244,25 @@
         <v>6</v>
       </c>
       <c r="K87" t="n">
-        <v>23.07759859367414</v>
+        <v>23.23111356074586</v>
       </c>
       <c r="L87" t="n">
         <v>15.02541767276855</v>
       </c>
       <c r="M87" t="n">
-        <v>17.99225470919088</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="N87" t="n">
-        <v>8.026213232574577</v>
+        <v>12.54816392343241</v>
       </c>
       <c r="O87" t="n">
-        <v>13.00923397088273</v>
+        <v>14.50866744077363</v>
       </c>
       <c r="P87" t="b">
         <v>1</v>
       </c>
       <c r="Q87" t="n">
-        <v>-77.39398526712966</v>
+        <v>-60.11886450343182</v>
       </c>
     </row>
     <row r="88">
@@ -5501,25 +5303,25 @@
         <v>6</v>
       </c>
       <c r="K88" t="n">
-        <v>23.03288491493475</v>
+        <v>23.01582633742614</v>
       </c>
       <c r="L88" t="n">
         <v>15.03855035193225</v>
       </c>
       <c r="M88" t="n">
-        <v>18.04864477364506</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="N88" t="n">
-        <v>8.026213232574577</v>
+        <v>12.54816392343241</v>
       </c>
       <c r="O88" t="n">
-        <v>13.03742900310982</v>
+        <v>14.50866744077363</v>
       </c>
       <c r="P88" t="b">
         <v>1</v>
       </c>
       <c r="Q88" t="n">
-        <v>-76.66738518338789</v>
+        <v>-58.63501201181918</v>
       </c>
     </row>
     <row r="89">
@@ -5560,25 +5362,25 @@
         <v>6</v>
       </c>
       <c r="K89" t="n">
-        <v>22.66480968815676</v>
+        <v>26.24216908963513</v>
       </c>
       <c r="L89" t="n">
         <v>15.12321741947181</v>
       </c>
       <c r="M89" t="n">
-        <v>18.06393349092241</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="N89" t="n">
-        <v>8.026213232574577</v>
+        <v>12.56367312450933</v>
       </c>
       <c r="O89" t="n">
-        <v>13.04507336174849</v>
+        <v>14.51642204131209</v>
       </c>
       <c r="P89" t="b">
         <v>1</v>
       </c>
       <c r="Q89" t="n">
-        <v>-73.74229381197507</v>
+        <v>-80.77573809133473</v>
       </c>
     </row>
     <row r="90">
@@ -5619,25 +5421,25 @@
         <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>22.62487457301624</v>
+        <v>24.43540424109552</v>
       </c>
       <c r="L90" t="n">
         <v>15.13058646677716</v>
       </c>
       <c r="M90" t="n">
-        <v>18.06393349092241</v>
+        <v>16.46917095811485</v>
       </c>
       <c r="N90" t="n">
-        <v>8.026213232574577</v>
+        <v>12.56367312450933</v>
       </c>
       <c r="O90" t="n">
-        <v>13.04507336174849</v>
+        <v>14.51642204131209</v>
       </c>
       <c r="P90" t="b">
         <v>1</v>
       </c>
       <c r="Q90" t="n">
-        <v>-73.43616203307977</v>
+        <v>-68.32938703183973</v>
       </c>
     </row>
     <row r="91">
@@ -5678,25 +5480,25 @@
         <v>6</v>
       </c>
       <c r="K91" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
       <c r="L91" t="n">
         <v>15.19769512414728</v>
       </c>
       <c r="M91" t="n">
-        <v>18.06393349092241</v>
+        <v>16.68150359318814</v>
       </c>
       <c r="N91" t="n">
-        <v>8.026213232574577</v>
+        <v>12.73286697894567</v>
       </c>
       <c r="O91" t="n">
-        <v>13.04507336174849</v>
+        <v>14.7071852860669</v>
       </c>
       <c r="P91" t="b">
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>-71.40246262722528</v>
+        <v>-52.22778137920483</v>
       </c>
     </row>
     <row r="92">
@@ -5737,25 +5539,25 @@
         <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>22.35957699356508</v>
+        <v>22.3884218643085</v>
       </c>
       <c r="L92" t="n">
         <v>15.19823595082566</v>
       </c>
       <c r="M92" t="n">
-        <v>18.06393349092241</v>
+        <v>16.68150359318814</v>
       </c>
       <c r="N92" t="n">
-        <v>8.026213232574577</v>
+        <v>12.73286697894567</v>
       </c>
       <c r="O92" t="n">
-        <v>13.04507336174849</v>
+        <v>14.7071852860669</v>
       </c>
       <c r="P92" t="b">
         <v>1</v>
       </c>
       <c r="Q92" t="n">
-        <v>-71.40246262722528</v>
+        <v>-52.22778137920483</v>
       </c>
     </row>
     <row r="93">
@@ -5796,25 +5598,25 @@
         <v>6</v>
       </c>
       <c r="K93" t="n">
-        <v>22.4810658565194</v>
+        <v>22.44510803430239</v>
       </c>
       <c r="L93" t="n">
         <v>15.58233221071537</v>
       </c>
       <c r="M93" t="n">
-        <v>18.26553935250956</v>
+        <v>17.13699864778113</v>
       </c>
       <c r="N93" t="n">
-        <v>8.33695754632191</v>
+        <v>12.90108600673018</v>
       </c>
       <c r="O93" t="n">
-        <v>13.30124844941573</v>
+        <v>15.01904232725565</v>
       </c>
       <c r="P93" t="b">
         <v>1</v>
       </c>
       <c r="Q93" t="n">
-        <v>-69.01470521368162</v>
+        <v>-49.44433569889048</v>
       </c>
     </row>
     <row r="94">
@@ -5855,25 +5657,25 @@
         <v>6</v>
       </c>
       <c r="K94" t="n">
-        <v>23.00388300949592</v>
+        <v>22.49401812226683</v>
       </c>
       <c r="L94" t="n">
         <v>15.59769100053833</v>
       </c>
       <c r="M94" t="n">
-        <v>18.26553935250956</v>
+        <v>17.65606000717672</v>
       </c>
       <c r="N94" t="n">
-        <v>8.33695754632191</v>
+        <v>12.90108600673018</v>
       </c>
       <c r="O94" t="n">
-        <v>13.30124844941573</v>
+        <v>15.27857300695345</v>
       </c>
       <c r="P94" t="b">
         <v>1</v>
       </c>
       <c r="Q94" t="n">
-        <v>-72.94529229326878</v>
+        <v>-47.22590985447101</v>
       </c>
     </row>
     <row r="95">
@@ -5914,25 +5716,25 @@
         <v>6</v>
       </c>
       <c r="K95" t="n">
-        <v>22.60724382801739</v>
+        <v>22.49694087128349</v>
       </c>
       <c r="L95" t="n">
         <v>15.64923011307725</v>
       </c>
       <c r="M95" t="n">
-        <v>18.26553935250956</v>
+        <v>17.65606000717672</v>
       </c>
       <c r="N95" t="n">
-        <v>8.659828082032606</v>
+        <v>12.73686903582316</v>
       </c>
       <c r="O95" t="n">
-        <v>13.46268371727108</v>
+        <v>15.19646452149994</v>
       </c>
       <c r="P95" t="b">
         <v>1</v>
       </c>
       <c r="Q95" t="n">
-        <v>-67.92523914837932</v>
+        <v>-48.04062378755825</v>
       </c>
     </row>
     <row r="96">
@@ -5973,25 +5775,25 @@
         <v>6</v>
       </c>
       <c r="K96" t="n">
-        <v>22.41499665150971</v>
+        <v>22.19039193738289</v>
       </c>
       <c r="L96" t="n">
         <v>15.80343622425014</v>
       </c>
       <c r="M96" t="n">
-        <v>18.25615665036968</v>
+        <v>17.65606000717672</v>
       </c>
       <c r="N96" t="n">
-        <v>8.659828082032606</v>
+        <v>12.73686903582316</v>
       </c>
       <c r="O96" t="n">
-        <v>13.45799236620114</v>
+        <v>15.19646452149994</v>
       </c>
       <c r="P96" t="b">
         <v>1</v>
       </c>
       <c r="Q96" t="n">
-        <v>-66.55527839206906</v>
+        <v>-46.02338528141166</v>
       </c>
     </row>
     <row r="97">
@@ -6032,25 +5834,25 @@
         <v>6</v>
       </c>
       <c r="K97" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
       <c r="L97" t="n">
         <v>15.89502070570716</v>
       </c>
       <c r="M97" t="n">
-        <v>18.25615665036968</v>
+        <v>17.72686803633449</v>
       </c>
       <c r="N97" t="n">
-        <v>8.659828082032606</v>
+        <v>12.73686903582316</v>
       </c>
       <c r="O97" t="n">
-        <v>13.45799236620114</v>
+        <v>15.23186853607882</v>
       </c>
       <c r="P97" t="b">
         <v>1</v>
       </c>
       <c r="Q97" t="n">
-        <v>-61.81464354133352</v>
+        <v>-42.87703661192304</v>
       </c>
     </row>
     <row r="98">
@@ -6091,25 +5893,25 @@
         <v>6</v>
       </c>
       <c r="K98" t="n">
-        <v>21.77700237518826</v>
+        <v>21.76284238497333</v>
       </c>
       <c r="L98" t="n">
         <v>15.89538858178903</v>
       </c>
       <c r="M98" t="n">
-        <v>18.25615665036968</v>
+        <v>17.72686803633449</v>
       </c>
       <c r="N98" t="n">
-        <v>8.659828082032606</v>
+        <v>12.73686903582316</v>
       </c>
       <c r="O98" t="n">
-        <v>13.45799236620114</v>
+        <v>15.23186853607882</v>
       </c>
       <c r="P98" t="b">
         <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>-61.81464354133352</v>
+        <v>-42.87703661192304</v>
       </c>
     </row>
     <row r="99">
@@ -6150,25 +5952,25 @@
         <v>6</v>
       </c>
       <c r="K99" t="n">
-        <v>25.95407996901959</v>
+        <v>21.65492269454226</v>
       </c>
       <c r="L99" t="n">
         <v>15.96942724531015</v>
       </c>
       <c r="M99" t="n">
-        <v>18.32865305918012</v>
+        <v>17.72686803633449</v>
       </c>
       <c r="N99" t="n">
-        <v>8.955520418282028</v>
+        <v>12.61285613536885</v>
       </c>
       <c r="O99" t="n">
-        <v>13.64208673873107</v>
+        <v>15.16986208585167</v>
       </c>
       <c r="P99" t="b">
         <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>-90.25007292567417</v>
+        <v>-42.74963458460805</v>
       </c>
     </row>
     <row r="100">
@@ -6209,25 +6011,25 @@
         <v>6</v>
       </c>
       <c r="K100" t="n">
-        <v>20.6651522369616</v>
+        <v>20.57281945073719</v>
       </c>
       <c r="L100" t="n">
         <v>16.24005843764725</v>
       </c>
       <c r="M100" t="n">
-        <v>18.32865305918012</v>
+        <v>17.82989940170764</v>
       </c>
       <c r="N100" t="n">
-        <v>9.182150333628899</v>
+        <v>12.48423020315763</v>
       </c>
       <c r="O100" t="n">
-        <v>13.75540169640451</v>
+        <v>15.15706480243264</v>
       </c>
       <c r="P100" t="b">
         <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>-50.23299713859473</v>
+        <v>-35.73089327582306</v>
       </c>
     </row>
     <row r="101">
@@ -6268,25 +6070,25 @@
         <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>20.58203948620306</v>
+        <v>20.50179656936968</v>
       </c>
       <c r="L101" t="n">
         <v>16.25358801320499</v>
       </c>
       <c r="M101" t="n">
-        <v>18.32865305918012</v>
+        <v>17.82989940170764</v>
       </c>
       <c r="N101" t="n">
-        <v>9.182150333628899</v>
+        <v>12.48423020315763</v>
       </c>
       <c r="O101" t="n">
-        <v>13.75540169640451</v>
+        <v>15.15706480243264</v>
       </c>
       <c r="P101" t="b">
         <v>1</v>
       </c>
       <c r="Q101" t="n">
-        <v>-49.62877813726772</v>
+        <v>-35.26231388863123</v>
       </c>
     </row>
     <row r="102">
@@ -6327,25 +6129,25 @@
         <v>6</v>
       </c>
       <c r="K102" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
       <c r="L102" t="n">
         <v>16.32316175370828</v>
       </c>
       <c r="M102" t="n">
-        <v>18.32865305918012</v>
+        <v>17.91105143658421</v>
       </c>
       <c r="N102" t="n">
-        <v>9.182150333628899</v>
+        <v>12.17615535638471</v>
       </c>
       <c r="O102" t="n">
-        <v>13.75540169640451</v>
+        <v>15.04360339648446</v>
       </c>
       <c r="P102" t="b">
         <v>1</v>
       </c>
       <c r="Q102" t="n">
-        <v>-45.78450500796995</v>
+        <v>-33.85605664905369</v>
       </c>
     </row>
     <row r="103">
@@ -6386,25 +6188,25 @@
         <v>6</v>
       </c>
       <c r="K103" t="n">
-        <v>20.05324427496122</v>
+        <v>20.1367742844572</v>
       </c>
       <c r="L103" t="n">
         <v>16.32343725831764</v>
       </c>
       <c r="M103" t="n">
-        <v>18.32865305918012</v>
+        <v>17.91105143658421</v>
       </c>
       <c r="N103" t="n">
-        <v>9.182150333628899</v>
+        <v>12.17615535638471</v>
       </c>
       <c r="O103" t="n">
-        <v>13.75540169640451</v>
+        <v>15.04360339648446</v>
       </c>
       <c r="P103" t="b">
         <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>-45.78450500796995</v>
+        <v>-33.85605664905369</v>
       </c>
     </row>
     <row r="104">
@@ -6445,25 +6247,25 @@
         <v>6</v>
       </c>
       <c r="K104" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
       <c r="L104" t="n">
         <v>16.5581859165251</v>
       </c>
       <c r="M104" t="n">
-        <v>18.22115293721825</v>
+        <v>18.11063187715624</v>
       </c>
       <c r="N104" t="n">
-        <v>9.502707810945383</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="O104" t="n">
-        <v>13.86193037408182</v>
+        <v>15.10229958799832</v>
       </c>
       <c r="P104" t="b">
         <v>1</v>
       </c>
       <c r="Q104" t="n">
-        <v>26.90146398088831</v>
+        <v>33.41700823314725</v>
       </c>
     </row>
     <row r="105">
@@ -6504,25 +6306,25 @@
         <v>6</v>
       </c>
       <c r="K105" t="n">
-        <v>10.13286816744238</v>
+        <v>10.05556289128236</v>
       </c>
       <c r="L105" t="n">
         <v>16.57971237588957</v>
       </c>
       <c r="M105" t="n">
-        <v>18.22115293721825</v>
+        <v>18.11063187715624</v>
       </c>
       <c r="N105" t="n">
-        <v>9.502707810945383</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="O105" t="n">
-        <v>13.86193037408182</v>
+        <v>15.10229958799832</v>
       </c>
       <c r="P105" t="b">
         <v>1</v>
       </c>
       <c r="Q105" t="n">
-        <v>26.90146398088831</v>
+        <v>33.41700823314725</v>
       </c>
     </row>
     <row r="106">
@@ -6563,25 +6365,25 @@
         <v>6</v>
       </c>
       <c r="K106" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
       <c r="L106" t="n">
         <v>16.78594121403185</v>
       </c>
       <c r="M106" t="n">
-        <v>18.30135144683257</v>
+        <v>18.25347872265014</v>
       </c>
       <c r="N106" t="n">
-        <v>9.666185798546529</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="O106" t="n">
-        <v>13.98376862268955</v>
+        <v>15.17372301074527</v>
       </c>
       <c r="P106" t="b">
         <v>1</v>
       </c>
       <c r="Q106" t="n">
-        <v>33.39810765753928</v>
+        <v>39.040744699504</v>
       </c>
     </row>
     <row r="107">
@@ -6622,25 +6424,25 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>9.313454523502497</v>
+        <v>9.249788548710319</v>
       </c>
       <c r="L107" t="n">
         <v>16.78677488031477</v>
       </c>
       <c r="M107" t="n">
-        <v>18.30135144683257</v>
+        <v>18.25347872265014</v>
       </c>
       <c r="N107" t="n">
-        <v>9.666185798546529</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="O107" t="n">
-        <v>13.98376862268955</v>
+        <v>15.17372301074527</v>
       </c>
       <c r="P107" t="b">
         <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>33.39810765753928</v>
+        <v>39.040744699504</v>
       </c>
     </row>
     <row r="108">
@@ -6681,25 +6483,25 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>9.006605764587595</v>
+        <v>9.001199936508684</v>
       </c>
       <c r="L108" t="n">
         <v>16.80349196838779</v>
       </c>
       <c r="M108" t="n">
-        <v>18.33354581660341</v>
+        <v>18.25347872265014</v>
       </c>
       <c r="N108" t="n">
-        <v>9.666185798546529</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="O108" t="n">
-        <v>13.99986580757497</v>
+        <v>15.17372301074527</v>
       </c>
       <c r="P108" t="b">
         <v>1</v>
       </c>
       <c r="Q108" t="n">
-        <v>35.66648503363259</v>
+        <v>40.67902827714408</v>
       </c>
     </row>
     <row r="109">
@@ -6740,25 +6542,25 @@
         <v>6</v>
       </c>
       <c r="K109" t="n">
-        <v>8.855391791179059</v>
+        <v>8.859202453554882</v>
       </c>
       <c r="L109" t="n">
         <v>17.48402535098008</v>
       </c>
       <c r="M109" t="n">
-        <v>21.13985137760104</v>
+        <v>18.18374248726346</v>
       </c>
       <c r="N109" t="n">
-        <v>10.03982707763049</v>
+        <v>13.12139488965561</v>
       </c>
       <c r="O109" t="n">
-        <v>15.58983922761577</v>
+        <v>15.65256868845954</v>
       </c>
       <c r="P109" t="b">
         <v>1</v>
       </c>
       <c r="Q109" t="n">
-        <v>43.19767085543344</v>
+        <v>43.40096740743471</v>
       </c>
     </row>
     <row r="110">
@@ -6799,25 +6601,25 @@
         <v>6</v>
       </c>
       <c r="K110" t="n">
-        <v>8.978645588225934</v>
+        <v>8.984742925862029</v>
       </c>
       <c r="L110" t="n">
         <v>17.62612145430888</v>
       </c>
       <c r="M110" t="n">
-        <v>21.25752534241971</v>
+        <v>18.18374248726346</v>
       </c>
       <c r="N110" t="n">
-        <v>10.10075936227274</v>
+        <v>13.40216427255851</v>
       </c>
       <c r="O110" t="n">
-        <v>15.67914235234623</v>
+        <v>15.79295337991098</v>
       </c>
       <c r="P110" t="b">
         <v>1</v>
       </c>
       <c r="Q110" t="n">
-        <v>42.73509745332231</v>
+        <v>43.10916577965184</v>
       </c>
     </row>
     <row r="111">
@@ -6858,25 +6660,25 @@
         <v>6</v>
       </c>
       <c r="K111" t="n">
-        <v>8.984199379338564</v>
+        <v>8.988563827679902</v>
       </c>
       <c r="L111" t="n">
         <v>17.64943709370389</v>
       </c>
       <c r="M111" t="n">
-        <v>21.25752534241971</v>
+        <v>18.18374248726346</v>
       </c>
       <c r="N111" t="n">
-        <v>10.10075936227274</v>
+        <v>13.40216427255851</v>
       </c>
       <c r="O111" t="n">
-        <v>15.67914235234623</v>
+        <v>15.79295337991098</v>
       </c>
       <c r="P111" t="b">
         <v>1</v>
       </c>
       <c r="Q111" t="n">
-        <v>42.69967592969669</v>
+        <v>43.08497206663338</v>
       </c>
     </row>
     <row r="112">
@@ -6917,25 +6719,25 @@
         <v>6</v>
       </c>
       <c r="K112" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
       <c r="L112" t="n">
         <v>18.03902319835816</v>
       </c>
       <c r="M112" t="n">
-        <v>21.24478764721551</v>
+        <v>18.58191783635835</v>
       </c>
       <c r="N112" t="n">
-        <v>10.3241301980949</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="O112" t="n">
-        <v>15.7844589226552</v>
+        <v>16.00513255111885</v>
       </c>
       <c r="P112" t="b">
         <v>1</v>
       </c>
       <c r="Q112" t="n">
-        <v>42.58922307036547</v>
+        <v>43.41144686513317</v>
       </c>
     </row>
     <row r="113">
@@ -6976,25 +6778,25 @@
         <v>6</v>
       </c>
       <c r="K113" t="n">
-        <v>9.061980501635373</v>
+        <v>9.057072937995757</v>
       </c>
       <c r="L113" t="n">
         <v>18.03910951510389</v>
       </c>
       <c r="M113" t="n">
-        <v>21.24478764721551</v>
+        <v>18.58191783635835</v>
       </c>
       <c r="N113" t="n">
-        <v>10.3241301980949</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="O113" t="n">
-        <v>15.7844589226552</v>
+        <v>16.00513255111885</v>
       </c>
       <c r="P113" t="b">
         <v>1</v>
       </c>
       <c r="Q113" t="n">
-        <v>42.58922307036547</v>
+        <v>43.41144686513317</v>
       </c>
     </row>
     <row r="114">
@@ -7035,25 +6837,25 @@
         <v>6</v>
       </c>
       <c r="K114" t="n">
-        <v>9.044872040221554</v>
+        <v>9.045523308623421</v>
       </c>
       <c r="L114" t="n">
         <v>18.04635251125015</v>
       </c>
       <c r="M114" t="n">
-        <v>21.24478764721551</v>
+        <v>18.58191783635835</v>
       </c>
       <c r="N114" t="n">
-        <v>10.3241301980949</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="O114" t="n">
-        <v>15.7844589226552</v>
+        <v>16.00513255111885</v>
       </c>
       <c r="P114" t="b">
         <v>1</v>
       </c>
       <c r="Q114" t="n">
-        <v>42.69761108352228</v>
+        <v>43.48360890025189</v>
       </c>
     </row>
     <row r="115">
@@ -7094,25 +6896,25 @@
         <v>6</v>
       </c>
       <c r="K115" t="n">
-        <v>8.817828618037916</v>
+        <v>8.809891251011997</v>
       </c>
       <c r="L115" t="n">
         <v>18.16606460055646</v>
       </c>
       <c r="M115" t="n">
-        <v>20.91401769073484</v>
+        <v>18.84045488162381</v>
       </c>
       <c r="N115" t="n">
-        <v>10.3241301980949</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="O115" t="n">
-        <v>15.61907394441487</v>
+        <v>16.13440107375158</v>
       </c>
       <c r="P115" t="b">
         <v>1</v>
       </c>
       <c r="Q115" t="n">
-        <v>43.54448509931647</v>
+        <v>45.39684980718334</v>
       </c>
     </row>
     <row r="116">
@@ -7153,25 +6955,25 @@
         <v>6</v>
       </c>
       <c r="K116" t="n">
-        <v>8.013828136438326</v>
+        <v>8.01349959414503</v>
       </c>
       <c r="L116" t="n">
         <v>18.48040920573799</v>
       </c>
       <c r="M116" t="n">
-        <v>21.75249733392203</v>
+        <v>18.54653760366034</v>
       </c>
       <c r="N116" t="n">
-        <v>10.72804752206529</v>
+        <v>12.3818195935645</v>
       </c>
       <c r="O116" t="n">
-        <v>16.24027242799366</v>
+        <v>15.46417859861242</v>
       </c>
       <c r="P116" t="b">
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>50.65459540798871</v>
+        <v>48.18024414911977</v>
       </c>
     </row>
     <row r="117">
@@ -7212,25 +7014,25 @@
         <v>6</v>
       </c>
       <c r="K117" t="n">
-        <v>7.881424971903225</v>
+        <v>7.879726061462629</v>
       </c>
       <c r="L117" t="n">
         <v>18.53568472460144</v>
       </c>
       <c r="M117" t="n">
-        <v>21.75249733392203</v>
+        <v>18.54653760366034</v>
       </c>
       <c r="N117" t="n">
-        <v>10.82821853712411</v>
+        <v>12.34488939642437</v>
       </c>
       <c r="O117" t="n">
-        <v>16.29035793552307</v>
+        <v>15.44571350004236</v>
       </c>
       <c r="P117" t="b">
         <v>1</v>
       </c>
       <c r="Q117" t="n">
-        <v>51.61908042108249</v>
+        <v>48.98438287463366</v>
       </c>
     </row>
     <row r="118">
@@ -7271,25 +7073,25 @@
         <v>6</v>
       </c>
       <c r="K118" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
       <c r="L118" t="n">
         <v>18.78592476439332</v>
       </c>
       <c r="M118" t="n">
-        <v>18.31538578099143</v>
+        <v>18.08007013293001</v>
       </c>
       <c r="N118" t="n">
-        <v>11.31153344108232</v>
+        <v>11.66917292052748</v>
       </c>
       <c r="O118" t="n">
-        <v>14.81345961103688</v>
+        <v>14.87462152672875</v>
       </c>
       <c r="P118" t="b">
         <v>1</v>
       </c>
       <c r="Q118" t="n">
-        <v>48.59543704217132</v>
+        <v>48.81649013375111</v>
       </c>
     </row>
     <row r="119">
@@ -7330,25 +7132,25 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
-        <v>7.614794171987974</v>
+        <v>7.613353376700388</v>
       </c>
       <c r="L119" t="n">
         <v>18.79314485270083</v>
       </c>
       <c r="M119" t="n">
-        <v>18.31538578099143</v>
+        <v>18.08007013293001</v>
       </c>
       <c r="N119" t="n">
-        <v>11.31153344108232</v>
+        <v>11.66917292052748</v>
       </c>
       <c r="O119" t="n">
-        <v>14.81345961103688</v>
+        <v>14.87462152672875</v>
       </c>
       <c r="P119" t="b">
         <v>1</v>
       </c>
       <c r="Q119" t="n">
-        <v>48.59543704217132</v>
+        <v>48.81649013375111</v>
       </c>
     </row>
     <row r="120">
@@ -7389,25 +7191,25 @@
         <v>6</v>
       </c>
       <c r="K120" t="n">
-        <v>7.525888632454506</v>
+        <v>7.52583147660655</v>
       </c>
       <c r="L120" t="n">
         <v>18.90843456010715</v>
       </c>
       <c r="M120" t="n">
-        <v>41.15307330033042</v>
+        <v>18.04915627873921</v>
       </c>
       <c r="N120" t="n">
-        <v>11.31153344108232</v>
+        <v>11.44003729032269</v>
       </c>
       <c r="O120" t="n">
-        <v>26.23230337070637</v>
+        <v>14.74459678453095</v>
       </c>
       <c r="P120" t="b">
         <v>1</v>
       </c>
       <c r="Q120" t="n">
-        <v>71.31060690286668</v>
+        <v>48.95871629055227</v>
       </c>
     </row>
     <row r="121">
@@ -7448,25 +7250,25 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
-        <v>7.648109426969325</v>
+        <v>7.649937527108574</v>
       </c>
       <c r="L121" t="n">
         <v>19.183341055718</v>
       </c>
       <c r="M121" t="n">
-        <v>55.6368087571851</v>
+        <v>17.98837875632599</v>
       </c>
       <c r="N121" t="n">
-        <v>11.56598692004501</v>
+        <v>11.37095695966775</v>
       </c>
       <c r="O121" t="n">
-        <v>33.60139783861506</v>
+        <v>14.67966785799687</v>
       </c>
       <c r="P121" t="b">
         <v>1</v>
       </c>
       <c r="Q121" t="n">
-        <v>77.23871648524086</v>
+        <v>47.88752987390511</v>
       </c>
     </row>
     <row r="122">
@@ -7507,25 +7309,25 @@
         <v>6</v>
       </c>
       <c r="K122" t="n">
-        <v>7.833439394377753</v>
+        <v>7.834451497123795</v>
       </c>
       <c r="L122" t="n">
         <v>19.39041118467946</v>
       </c>
       <c r="M122" t="n">
-        <v>42.99916497611289</v>
+        <v>17.74861576103778</v>
       </c>
       <c r="N122" t="n">
-        <v>11.6068897425725</v>
+        <v>11.0824964530113</v>
       </c>
       <c r="O122" t="n">
-        <v>27.30302735934269</v>
+        <v>14.41555610702454</v>
       </c>
       <c r="P122" t="b">
         <v>1</v>
       </c>
       <c r="Q122" t="n">
-        <v>71.30926438566796</v>
+        <v>45.65279730480773</v>
       </c>
     </row>
     <row r="123">
@@ -7566,25 +7368,25 @@
         <v>6</v>
       </c>
       <c r="K123" t="n">
-        <v>7.877726027147521</v>
+        <v>7.878513743038085</v>
       </c>
       <c r="L123" t="n">
         <v>19.48300435474419</v>
       </c>
       <c r="M123" t="n">
-        <v>40.56424938189363</v>
+        <v>17.74861576103778</v>
       </c>
       <c r="N123" t="n">
-        <v>11.6490487157816</v>
+        <v>11.11346172376633</v>
       </c>
       <c r="O123" t="n">
-        <v>26.10664904883762</v>
+        <v>14.43103874240205</v>
       </c>
       <c r="P123" t="b">
         <v>1</v>
       </c>
       <c r="Q123" t="n">
-        <v>69.82482886865071</v>
+        <v>45.40577512352585</v>
       </c>
     </row>
     <row r="124">
@@ -7625,25 +7427,25 @@
         <v>6</v>
       </c>
       <c r="K124" t="n">
-        <v>7.996504394876585</v>
+        <v>7.996384831667157</v>
       </c>
       <c r="L124" t="n">
         <v>19.88977015831271</v>
       </c>
       <c r="M124" t="n">
-        <v>23.51115280153341</v>
+        <v>17.97859383075771</v>
       </c>
       <c r="N124" t="n">
-        <v>12.28759492419801</v>
+        <v>11.38295853545234</v>
       </c>
       <c r="O124" t="n">
-        <v>17.89937386286571</v>
+        <v>14.68077618310502</v>
       </c>
       <c r="P124" t="b">
         <v>1</v>
       </c>
       <c r="Q124" t="n">
-        <v>55.32522837870746</v>
+        <v>45.53159361649023</v>
       </c>
     </row>
     <row r="125">
@@ -7684,25 +7486,25 @@
         <v>6</v>
       </c>
       <c r="K125" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
       <c r="L125" t="n">
         <v>20.03843725449725</v>
       </c>
       <c r="M125" t="n">
-        <v>23.03288491493475</v>
+        <v>18.04209307204975</v>
       </c>
       <c r="N125" t="n">
-        <v>12.54621779554327</v>
+        <v>11.40906398075885</v>
       </c>
       <c r="O125" t="n">
-        <v>17.78955135523901</v>
+        <v>14.7255785264043</v>
       </c>
       <c r="P125" t="b">
         <v>1</v>
       </c>
       <c r="Q125" t="n">
-        <v>54.88243029686713</v>
+        <v>45.48992208629959</v>
       </c>
     </row>
     <row r="126">
@@ -7743,25 +7545,25 @@
         <v>6</v>
       </c>
       <c r="K126" t="n">
-        <v>8.026213232574577</v>
+        <v>8.026924327986121</v>
       </c>
       <c r="L126" t="n">
         <v>20.04821132778157</v>
       </c>
       <c r="M126" t="n">
-        <v>23.03288491493475</v>
+        <v>18.04209307204975</v>
       </c>
       <c r="N126" t="n">
-        <v>12.54621779554327</v>
+        <v>11.40906398075885</v>
       </c>
       <c r="O126" t="n">
-        <v>17.78955135523901</v>
+        <v>14.7255785264043</v>
       </c>
       <c r="P126" t="b">
         <v>1</v>
       </c>
       <c r="Q126" t="n">
-        <v>54.88243029686713</v>
+        <v>45.48992208629959</v>
       </c>
     </row>
     <row r="127">
@@ -7802,25 +7604,25 @@
         <v>6</v>
       </c>
       <c r="K127" t="n">
-        <v>8.218318514120106</v>
+        <v>8.215642482556708</v>
       </c>
       <c r="L127" t="n">
         <v>20.35503558194549</v>
       </c>
       <c r="M127" t="n">
-        <v>22.35957699356508</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="N127" t="n">
-        <v>12.90081744954813</v>
+        <v>11.63801176927609</v>
       </c>
       <c r="O127" t="n">
-        <v>17.63019722155661</v>
+        <v>14.94669398373369</v>
       </c>
       <c r="P127" t="b">
         <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>53.38498820607922</v>
+        <v>45.03371453581845</v>
       </c>
     </row>
     <row r="128">
@@ -7861,25 +7663,25 @@
         <v>6</v>
       </c>
       <c r="K128" t="n">
-        <v>8.233471211243319</v>
+        <v>8.234901432720093</v>
       </c>
       <c r="L128" t="n">
         <v>20.37936653809992</v>
       </c>
       <c r="M128" t="n">
-        <v>22.35957699356508</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="N128" t="n">
-        <v>12.90081744954813</v>
+        <v>11.63801176927609</v>
       </c>
       <c r="O128" t="n">
-        <v>17.63019722155661</v>
+        <v>14.94669398373369</v>
       </c>
       <c r="P128" t="b">
         <v>1</v>
       </c>
       <c r="Q128" t="n">
-        <v>53.29904080042748</v>
+        <v>44.90486363284055</v>
       </c>
     </row>
     <row r="129">
@@ -7920,25 +7722,25 @@
         <v>6</v>
       </c>
       <c r="K129" t="n">
-        <v>8.33695754632191</v>
+        <v>8.338770570052079</v>
       </c>
       <c r="L129" t="n">
         <v>20.49463435150532</v>
       </c>
       <c r="M129" t="n">
-        <v>22.4810658565194</v>
+        <v>18.25537619819129</v>
       </c>
       <c r="N129" t="n">
-        <v>12.90081744954813</v>
+        <v>11.63801176927609</v>
       </c>
       <c r="O129" t="n">
-        <v>17.69094165303377</v>
+        <v>14.94669398373369</v>
       </c>
       <c r="P129" t="b">
         <v>1</v>
       </c>
       <c r="Q129" t="n">
-        <v>52.87442743392786</v>
+        <v>44.20993311880831</v>
       </c>
     </row>
     <row r="130">
@@ -7979,25 +7781,25 @@
         <v>6</v>
       </c>
       <c r="K130" t="n">
-        <v>8.659828082032606</v>
+        <v>8.661114516403142</v>
       </c>
       <c r="L130" t="n">
         <v>20.78903289049731</v>
       </c>
       <c r="M130" t="n">
-        <v>22.41499665150971</v>
+        <v>18.25543714052691</v>
       </c>
       <c r="N130" t="n">
-        <v>12.73729214372356</v>
+        <v>12.32493800141896</v>
       </c>
       <c r="O130" t="n">
-        <v>17.57614439761664</v>
+        <v>15.29018757097293</v>
       </c>
       <c r="P130" t="b">
         <v>1</v>
       </c>
       <c r="Q130" t="n">
-        <v>50.72964874362948</v>
+        <v>43.35508000669984</v>
       </c>
     </row>
     <row r="131">
@@ -8038,25 +7840,25 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
-        <v>8.955520418282028</v>
+        <v>8.957982002673143</v>
       </c>
       <c r="L131" t="n">
         <v>21.05154437345794</v>
       </c>
       <c r="M131" t="n">
-        <v>25.95407996901959</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="N131" t="n">
-        <v>12.61379930677621</v>
+        <v>12.68439321587084</v>
       </c>
       <c r="O131" t="n">
-        <v>19.2839396378979</v>
+        <v>15.51760904217408</v>
       </c>
       <c r="P131" t="b">
         <v>1</v>
       </c>
       <c r="Q131" t="n">
-        <v>53.55969482147659</v>
+        <v>42.27215044323548</v>
       </c>
     </row>
     <row r="132">
@@ -8097,25 +7899,25 @@
         <v>6</v>
       </c>
       <c r="K132" t="n">
-        <v>9.117370986390577</v>
+        <v>9.118840462178738</v>
       </c>
       <c r="L132" t="n">
         <v>21.21457518786828</v>
       </c>
       <c r="M132" t="n">
-        <v>20.6651522369616</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="N132" t="n">
-        <v>12.48481118538775</v>
+        <v>13.02958147828541</v>
       </c>
       <c r="O132" t="n">
-        <v>16.57498171117467</v>
+        <v>15.69020317338137</v>
       </c>
       <c r="P132" t="b">
         <v>1</v>
       </c>
       <c r="Q132" t="n">
-        <v>44.99317619009048</v>
+        <v>41.8819478536201</v>
       </c>
     </row>
     <row r="133">
@@ -8156,25 +7958,25 @@
         <v>6</v>
       </c>
       <c r="K133" t="n">
-        <v>9.182150333628899</v>
+        <v>9.184142659321292</v>
       </c>
       <c r="L133" t="n">
         <v>21.2512787523155</v>
       </c>
       <c r="M133" t="n">
-        <v>20.58203948620306</v>
+        <v>18.35082486847733</v>
       </c>
       <c r="N133" t="n">
-        <v>12.48481118538775</v>
+        <v>13.10942074896131</v>
       </c>
       <c r="O133" t="n">
-        <v>16.53342533579541</v>
+        <v>15.73012280871932</v>
       </c>
       <c r="P133" t="b">
         <v>1</v>
       </c>
       <c r="Q133" t="n">
-        <v>44.46310944563167</v>
+        <v>41.6142977966424</v>
       </c>
     </row>
     <row r="134">
@@ -8215,25 +8017,25 @@
         <v>6</v>
       </c>
       <c r="K134" t="n">
-        <v>9.502707810945383</v>
+        <v>9.503947719470569</v>
       </c>
       <c r="L134" t="n">
         <v>21.53516333167102</v>
       </c>
       <c r="M134" t="n">
-        <v>10.13286816744238</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="N134" t="n">
-        <v>12.09432674237669</v>
+        <v>13.41609389853743</v>
       </c>
       <c r="O134" t="n">
-        <v>11.11359745490953</v>
+        <v>15.86725916205331</v>
       </c>
       <c r="P134" t="b">
         <v>1</v>
       </c>
       <c r="Q134" t="n">
-        <v>14.49476328884422</v>
+        <v>40.10340650262181</v>
       </c>
     </row>
     <row r="135">
@@ -8274,25 +8076,25 @@
         <v>6</v>
       </c>
       <c r="K135" t="n">
-        <v>9.58700817278682</v>
+        <v>9.601021663415642</v>
       </c>
       <c r="L135" t="n">
         <v>21.68214617778379</v>
       </c>
       <c r="M135" t="n">
-        <v>10.13286816744238</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="N135" t="n">
-        <v>12.09432674237669</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="O135" t="n">
-        <v>11.11359745490953</v>
+        <v>16.0876374263895</v>
       </c>
       <c r="P135" t="b">
         <v>1</v>
       </c>
       <c r="Q135" t="n">
-        <v>13.7362297700312</v>
+        <v>40.32049946832764</v>
       </c>
     </row>
     <row r="136">
@@ -8333,25 +8135,25 @@
         <v>6</v>
       </c>
       <c r="K136" t="n">
-        <v>9.600055061876473</v>
+        <v>9.601021663415642</v>
       </c>
       <c r="L136" t="n">
         <v>21.68392616637894</v>
       </c>
       <c r="M136" t="n">
-        <v>9.313454523502497</v>
+        <v>18.31842442556919</v>
       </c>
       <c r="N136" t="n">
-        <v>12.09432674237669</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="O136" t="n">
-        <v>10.70389063293959</v>
+        <v>16.0876374263895</v>
       </c>
       <c r="P136" t="b">
         <v>1</v>
       </c>
       <c r="Q136" t="n">
-        <v>10.31247056716214</v>
+        <v>40.32049946832764</v>
       </c>
     </row>
     <row r="137">
@@ -8392,25 +8194,25 @@
         <v>6</v>
       </c>
       <c r="K137" t="n">
-        <v>9.666185798546529</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="L137" t="n">
         <v>21.80640445348596</v>
       </c>
       <c r="M137" t="n">
-        <v>9.006605764587595</v>
+        <v>18.3533122614999</v>
       </c>
       <c r="N137" t="n">
-        <v>12.09432674237669</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="O137" t="n">
-        <v>10.55046625348214</v>
+        <v>16.10508134435485</v>
       </c>
       <c r="P137" t="b">
         <v>1</v>
       </c>
       <c r="Q137" t="n">
-        <v>8.381434845533576</v>
+        <v>39.97496621993686</v>
       </c>
     </row>
     <row r="138">
@@ -8451,25 +8253,25 @@
         <v>6</v>
       </c>
       <c r="K138" t="n">
-        <v>9.747179920199084</v>
+        <v>9.748095555311115</v>
       </c>
       <c r="L138" t="n">
         <v>21.92999840691627</v>
       </c>
       <c r="M138" t="n">
-        <v>9.006605764587595</v>
+        <v>18.62276903281257</v>
       </c>
       <c r="N138" t="n">
-        <v>12.31599521887282</v>
+        <v>13.90173162460115</v>
       </c>
       <c r="O138" t="n">
-        <v>10.66130049173021</v>
+        <v>16.26225032870686</v>
       </c>
       <c r="P138" t="b">
         <v>1</v>
       </c>
       <c r="Q138" t="n">
-        <v>8.574193854119327</v>
+        <v>40.05690874095489</v>
       </c>
     </row>
     <row r="139">
@@ -8510,25 +8312,25 @@
         <v>6</v>
       </c>
       <c r="K139" t="n">
-        <v>9.919536055839442</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="L139" t="n">
         <v>22.31613211330096</v>
       </c>
       <c r="M139" t="n">
-        <v>8.855391791179059</v>
+        <v>19.95730210915573</v>
       </c>
       <c r="N139" t="n">
-        <v>12.5062115616939</v>
+        <v>12.78976864218879</v>
       </c>
       <c r="O139" t="n">
-        <v>10.68080167643648</v>
+        <v>16.37353537567226</v>
       </c>
       <c r="P139" t="b">
         <v>1</v>
       </c>
       <c r="Q139" t="n">
-        <v>7.127420241090232</v>
+        <v>39.41148674370719</v>
       </c>
     </row>
     <row r="140">
@@ -8569,25 +8371,25 @@
         <v>6</v>
       </c>
       <c r="K140" t="n">
-        <v>10.03982707763049</v>
+        <v>10.03384085376461</v>
       </c>
       <c r="L140" t="n">
         <v>22.5501686225714</v>
       </c>
       <c r="M140" t="n">
-        <v>8.855391791179059</v>
+        <v>21.00429376107303</v>
       </c>
       <c r="N140" t="n">
-        <v>13.18008131564125</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="O140" t="n">
-        <v>11.01773655341016</v>
+        <v>16.51387166432249</v>
       </c>
       <c r="P140" t="b">
         <v>1</v>
       </c>
       <c r="Q140" t="n">
-        <v>8.875774720507245</v>
+        <v>39.23992472678415</v>
       </c>
     </row>
     <row r="141">
@@ -8628,25 +8430,25 @@
         <v>6</v>
       </c>
       <c r="K141" t="n">
-        <v>10.10075936227274</v>
+        <v>10.04873175068141</v>
       </c>
       <c r="L141" t="n">
         <v>22.62995801969953</v>
       </c>
       <c r="M141" t="n">
-        <v>8.978645588225934</v>
+        <v>21.19153026999809</v>
       </c>
       <c r="N141" t="n">
-        <v>13.40114512882637</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="O141" t="n">
-        <v>11.18989535852615</v>
+        <v>16.60748991878501</v>
       </c>
       <c r="P141" t="b">
         <v>1</v>
       </c>
       <c r="Q141" t="n">
-        <v>9.733209841176427</v>
+        <v>39.49277223817476</v>
       </c>
     </row>
     <row r="142">
@@ -8687,25 +8489,25 @@
         <v>6</v>
       </c>
       <c r="K142" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
       <c r="L142" t="n">
         <v>22.80401154053545</v>
       </c>
       <c r="M142" t="n">
-        <v>8.984199379338564</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="N142" t="n">
-        <v>13.51724608384559</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="O142" t="n">
-        <v>11.25072273159208</v>
+        <v>16.27878943706481</v>
       </c>
       <c r="P142" t="b">
         <v>1</v>
       </c>
       <c r="Q142" t="n">
-        <v>9.470360628151353</v>
+        <v>37.52415422856537</v>
       </c>
     </row>
     <row r="143">
@@ -8746,25 +8548,25 @@
         <v>6</v>
       </c>
       <c r="K143" t="n">
-        <v>10.18523871563691</v>
+        <v>10.1703113821572</v>
       </c>
       <c r="L143" t="n">
         <v>22.80784059220252</v>
       </c>
       <c r="M143" t="n">
-        <v>8.984199379338564</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="N143" t="n">
-        <v>13.51724608384559</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="O143" t="n">
-        <v>11.25072273159208</v>
+        <v>16.27878943706481</v>
       </c>
       <c r="P143" t="b">
         <v>1</v>
       </c>
       <c r="Q143" t="n">
-        <v>9.470360628151353</v>
+        <v>37.52415422856537</v>
       </c>
     </row>
     <row r="144">
@@ -8805,25 +8607,25 @@
         <v>6</v>
       </c>
       <c r="K144" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
       <c r="L144" t="n">
         <v>22.99516598229082</v>
       </c>
       <c r="M144" t="n">
-        <v>9.061980501635373</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="N144" t="n">
-        <v>13.45049177307704</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="O144" t="n">
-        <v>11.25623613735621</v>
+        <v>16.27878943706481</v>
       </c>
       <c r="P144" t="b">
         <v>1</v>
       </c>
       <c r="Q144" t="n">
-        <v>8.280795888493452</v>
+        <v>36.56454162659087</v>
       </c>
     </row>
     <row r="145">
@@ -8864,25 +8666,25 @@
         <v>6</v>
       </c>
       <c r="K145" t="n">
-        <v>10.3241301980949</v>
+        <v>10.32652469704417</v>
       </c>
       <c r="L145" t="n">
         <v>22.99640523647197</v>
       </c>
       <c r="M145" t="n">
-        <v>9.061980501635373</v>
+        <v>21.20271511536878</v>
       </c>
       <c r="N145" t="n">
-        <v>13.45049177307704</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="O145" t="n">
-        <v>11.25623613735621</v>
+        <v>16.27878943706481</v>
       </c>
       <c r="P145" t="b">
         <v>1</v>
       </c>
       <c r="Q145" t="n">
-        <v>8.280795888493452</v>
+        <v>36.56454162659087</v>
       </c>
     </row>
     <row r="146">
@@ -8923,25 +8725,25 @@
         <v>6</v>
       </c>
       <c r="K146" t="n">
-        <v>10.72804752206529</v>
+        <v>10.73329757505697</v>
       </c>
       <c r="L146" t="n">
         <v>23.45554106369958</v>
       </c>
       <c r="M146" t="n">
-        <v>8.013828136438326</v>
+        <v>22.81637576394737</v>
       </c>
       <c r="N146" t="n">
-        <v>12.383252203665</v>
+        <v>9.795415074047549</v>
       </c>
       <c r="O146" t="n">
-        <v>10.19854017005166</v>
+        <v>16.30589541899746</v>
       </c>
       <c r="P146" t="b">
         <v>1</v>
       </c>
       <c r="Q146" t="n">
-        <v>-5.191991630023085</v>
+        <v>34.17535621777655</v>
       </c>
     </row>
     <row r="147">
@@ -8982,25 +8784,25 @@
         <v>6</v>
       </c>
       <c r="K147" t="n">
-        <v>10.82821853712411</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="L147" t="n">
         <v>23.55214805798182</v>
       </c>
       <c r="M147" t="n">
-        <v>7.881424971903225</v>
+        <v>22.81637576394737</v>
       </c>
       <c r="N147" t="n">
-        <v>12.32503009871696</v>
+        <v>11.14361891424003</v>
       </c>
       <c r="O147" t="n">
-        <v>10.10322753531009</v>
+        <v>16.9799973390937</v>
       </c>
       <c r="P147" t="b">
         <v>1</v>
       </c>
       <c r="Q147" t="n">
-        <v>-7.175835635495909</v>
+        <v>36.2069752169303</v>
       </c>
     </row>
     <row r="148">
@@ -9041,25 +8843,25 @@
         <v>6</v>
       </c>
       <c r="K148" t="n">
-        <v>11.31153344108232</v>
+        <v>11.34493953621662</v>
       </c>
       <c r="L148" t="n">
         <v>23.99585606920327</v>
       </c>
       <c r="M148" t="n">
-        <v>7.525888632454506</v>
+        <v>0.8260418668445116</v>
       </c>
       <c r="N148" t="n">
-        <v>11.37121225770263</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="O148" t="n">
-        <v>9.448550445078569</v>
+        <v>6.410889188787917</v>
       </c>
       <c r="P148" t="b">
         <v>1</v>
       </c>
       <c r="Q148" t="n">
-        <v>-19.71713022894555</v>
+        <v>-76.96358807851378</v>
       </c>
     </row>
     <row r="149">
@@ -9100,25 +8902,25 @@
         <v>6</v>
       </c>
       <c r="K149" t="n">
-        <v>11.3428515747395</v>
+        <v>11.34493953621662</v>
       </c>
       <c r="L149" t="n">
         <v>24.00389868149255</v>
       </c>
       <c r="M149" t="n">
-        <v>7.525888632454506</v>
+        <v>0.8260418668445116</v>
       </c>
       <c r="N149" t="n">
-        <v>11.37121225770263</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="O149" t="n">
-        <v>9.448550445078569</v>
+        <v>6.410889188787917</v>
       </c>
       <c r="P149" t="b">
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>-20.04858989399383</v>
+        <v>-76.96358807851378</v>
       </c>
     </row>
     <row r="150">
@@ -9159,25 +8961,25 @@
         <v>6</v>
       </c>
       <c r="K150" t="n">
-        <v>11.56598692004501</v>
+        <v>11.56684451772449</v>
       </c>
       <c r="L150" t="n">
         <v>24.23505888063864</v>
       </c>
       <c r="M150" t="n">
-        <v>7.648109426969325</v>
+        <v>56.23003942877807</v>
       </c>
       <c r="N150" t="n">
-        <v>11.08346970895239</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="O150" t="n">
-        <v>9.36578956796086</v>
+        <v>34.11288796975469</v>
       </c>
       <c r="P150" t="b">
         <v>1</v>
       </c>
       <c r="Q150" t="n">
-        <v>-23.49185123281801</v>
+        <v>66.0924500793368</v>
       </c>
     </row>
     <row r="151">
@@ -9218,25 +9020,25 @@
         <v>6</v>
       </c>
       <c r="K151" t="n">
-        <v>11.58221626307304</v>
+        <v>11.58198326305179</v>
       </c>
       <c r="L151" t="n">
         <v>24.29168241502517</v>
       </c>
       <c r="M151" t="n">
-        <v>7.833439394377753</v>
+        <v>45.66360168374498</v>
       </c>
       <c r="N151" t="n">
-        <v>11.08346970895239</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="O151" t="n">
-        <v>9.458454551665074</v>
+        <v>28.82966909723815</v>
       </c>
       <c r="P151" t="b">
         <v>1</v>
       </c>
       <c r="Q151" t="n">
-        <v>-22.45358054856963</v>
+        <v>59.82616649539927</v>
       </c>
     </row>
     <row r="152">
@@ -9277,25 +9079,25 @@
         <v>6</v>
       </c>
       <c r="K152" t="n">
-        <v>11.6068897425725</v>
+        <v>11.60728634568303</v>
       </c>
       <c r="L152" t="n">
         <v>24.44008764658244</v>
       </c>
       <c r="M152" t="n">
-        <v>7.877726027147521</v>
+        <v>40.59325963239543</v>
       </c>
       <c r="N152" t="n">
-        <v>11.08346970895239</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="O152" t="n">
-        <v>9.480597868049959</v>
+        <v>26.29449807156337</v>
       </c>
       <c r="P152" t="b">
         <v>1</v>
       </c>
       <c r="Q152" t="n">
-        <v>-22.42782474392504</v>
+        <v>55.8565966382301</v>
       </c>
     </row>
     <row r="153">
@@ -9336,25 +9138,25 @@
         <v>6</v>
       </c>
       <c r="K153" t="n">
-        <v>11.6490487157816</v>
+        <v>11.65030216584749</v>
       </c>
       <c r="L153" t="n">
         <v>24.4815099418555</v>
       </c>
       <c r="M153" t="n">
-        <v>7.877726027147521</v>
+        <v>40.59325963239543</v>
       </c>
       <c r="N153" t="n">
-        <v>11.1133397312677</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="O153" t="n">
-        <v>9.495532879207609</v>
+        <v>27.8189269577507</v>
       </c>
       <c r="P153" t="b">
         <v>1</v>
       </c>
       <c r="Q153" t="n">
-        <v>-22.67925206482673</v>
+        <v>58.12095059043398</v>
       </c>
     </row>
     <row r="154">
@@ -9395,25 +9197,25 @@
         <v>6</v>
       </c>
       <c r="K154" t="n">
-        <v>12.28759492419801</v>
+        <v>12.28927385385947</v>
       </c>
       <c r="L154" t="n">
         <v>24.94180141280403</v>
       </c>
       <c r="M154" t="n">
-        <v>7.996504394876585</v>
+        <v>23.49332569301106</v>
       </c>
       <c r="N154" t="n">
-        <v>11.40930901230741</v>
+        <v>18.75529113087354</v>
       </c>
       <c r="O154" t="n">
-        <v>9.702906703591998</v>
+        <v>21.1243084119423</v>
       </c>
       <c r="P154" t="b">
         <v>1</v>
       </c>
       <c r="Q154" t="n">
-        <v>-26.63828788180729</v>
+        <v>41.82401802602013</v>
       </c>
     </row>
     <row r="155">
@@ -9454,25 +9256,25 @@
         <v>6</v>
       </c>
       <c r="K155" t="n">
-        <v>12.54621779554327</v>
+        <v>12.54816392343241</v>
       </c>
       <c r="L155" t="n">
         <v>25.06599781876174</v>
       </c>
       <c r="M155" t="n">
-        <v>8.026213232574577</v>
+        <v>23.01582633742614</v>
       </c>
       <c r="N155" t="n">
-        <v>11.40930901230741</v>
+        <v>18.75529113087354</v>
       </c>
       <c r="O155" t="n">
-        <v>9.717761122440994</v>
+        <v>20.88555873414984</v>
       </c>
       <c r="P155" t="b">
         <v>1</v>
       </c>
       <c r="Q155" t="n">
-        <v>-29.10605269531259</v>
+        <v>39.91942431056448</v>
       </c>
     </row>
     <row r="156">
@@ -9513,25 +9315,25 @@
         <v>6</v>
       </c>
       <c r="K156" t="n">
-        <v>12.57078394962207</v>
+        <v>12.56367312450933</v>
       </c>
       <c r="L156" t="n">
         <v>25.1030654038451</v>
       </c>
       <c r="M156" t="n">
-        <v>8.026213232574577</v>
+        <v>26.24216908963513</v>
       </c>
       <c r="N156" t="n">
-        <v>11.40930901230741</v>
+        <v>18.75529113087354</v>
       </c>
       <c r="O156" t="n">
-        <v>9.717761122440994</v>
+        <v>22.49873011025434</v>
       </c>
       <c r="P156" t="b">
         <v>1</v>
       </c>
       <c r="Q156" t="n">
-        <v>-29.35884913442312</v>
+        <v>44.15830109992236</v>
       </c>
     </row>
     <row r="157">
@@ -9572,25 +9374,25 @@
         <v>6</v>
       </c>
       <c r="K157" t="n">
-        <v>12.73187879407693</v>
+        <v>12.73286697894567</v>
       </c>
       <c r="L157" t="n">
         <v>25.22668052718002</v>
       </c>
       <c r="M157" t="n">
-        <v>8.218318514120106</v>
+        <v>22.3884218643085</v>
       </c>
       <c r="N157" t="n">
-        <v>11.63847912745985</v>
+        <v>19.78860372735059</v>
       </c>
       <c r="O157" t="n">
-        <v>9.928398820789978</v>
+        <v>21.08851279582955</v>
       </c>
       <c r="P157" t="b">
         <v>1</v>
       </c>
       <c r="Q157" t="n">
-        <v>-28.23697983824429</v>
+        <v>39.62178792682</v>
       </c>
     </row>
     <row r="158">
@@ -9631,25 +9433,25 @@
         <v>6</v>
       </c>
       <c r="K158" t="n">
-        <v>12.90081744954813</v>
+        <v>12.90108600673018</v>
       </c>
       <c r="L158" t="n">
         <v>25.43021389350719</v>
       </c>
       <c r="M158" t="n">
-        <v>8.233471211243319</v>
+        <v>22.44510803430239</v>
       </c>
       <c r="N158" t="n">
-        <v>11.63847912745985</v>
+        <v>25.70526768557929</v>
       </c>
       <c r="O158" t="n">
-        <v>9.935975169351584</v>
+        <v>24.07518785994084</v>
       </c>
       <c r="P158" t="b">
         <v>1</v>
       </c>
       <c r="Q158" t="n">
-        <v>-29.83946950010377</v>
+        <v>46.41335269413811</v>
       </c>
     </row>
     <row r="159">
@@ -9690,25 +9492,25 @@
         <v>6</v>
       </c>
       <c r="K159" t="n">
-        <v>12.73729214372356</v>
+        <v>12.73686903582316</v>
       </c>
       <c r="L159" t="n">
         <v>25.82060381775251</v>
       </c>
       <c r="M159" t="n">
-        <v>8.659828082032606</v>
+        <v>22.19039193738289</v>
       </c>
       <c r="N159" t="n">
-        <v>12.32498885385217</v>
+        <v>32.72010281853873</v>
       </c>
       <c r="O159" t="n">
-        <v>10.49240846794239</v>
+        <v>27.45524737796081</v>
       </c>
       <c r="P159" t="b">
         <v>1</v>
       </c>
       <c r="Q159" t="n">
-        <v>-21.39531340816554</v>
+        <v>53.60861674097519</v>
       </c>
     </row>
     <row r="160">
@@ -9749,25 +9551,25 @@
         <v>6</v>
       </c>
       <c r="K160" t="n">
-        <v>12.61379930677621</v>
+        <v>12.61285613536885</v>
       </c>
       <c r="L160" t="n">
         <v>25.97720755312211</v>
       </c>
       <c r="M160" t="n">
-        <v>8.955520418282028</v>
+        <v>21.65492269454226</v>
       </c>
       <c r="N160" t="n">
-        <v>12.6846002976039</v>
+        <v>31.86592787966785</v>
       </c>
       <c r="O160" t="n">
-        <v>10.82006035794296</v>
+        <v>26.76042528710506</v>
       </c>
       <c r="P160" t="b">
         <v>1</v>
       </c>
       <c r="Q160" t="n">
-        <v>-16.57790150418592</v>
+        <v>52.86750490678278</v>
       </c>
     </row>
     <row r="161">
@@ -9808,25 +9610,25 @@
         <v>6</v>
       </c>
       <c r="K161" t="n">
-        <v>12.48481118538775</v>
+        <v>12.48423020315763</v>
       </c>
       <c r="L161" t="n">
         <v>26.14253635112133</v>
       </c>
       <c r="M161" t="n">
-        <v>9.117370986390577</v>
+        <v>20.57281945073719</v>
       </c>
       <c r="N161" t="n">
-        <v>13.02992558520946</v>
+        <v>31.86592787966785</v>
       </c>
       <c r="O161" t="n">
-        <v>11.07364828580002</v>
+        <v>26.21937366520252</v>
       </c>
       <c r="P161" t="b">
         <v>1</v>
       </c>
       <c r="Q161" t="n">
-        <v>-12.7434325451468</v>
+        <v>52.3854750972702</v>
       </c>
     </row>
     <row r="162">
@@ -9867,25 +9669,25 @@
         <v>6</v>
       </c>
       <c r="K162" t="n">
-        <v>12.17667309377143</v>
+        <v>12.17615535638471</v>
       </c>
       <c r="L162" t="n">
         <v>26.44482551477647</v>
       </c>
       <c r="M162" t="n">
-        <v>9.502707810945383</v>
+        <v>10.05556289128236</v>
       </c>
       <c r="N162" t="n">
-        <v>13.38869754162123</v>
+        <v>27.77808184280534</v>
       </c>
       <c r="O162" t="n">
-        <v>11.4457026762833</v>
+        <v>18.91682236704385</v>
       </c>
       <c r="P162" t="b">
         <v>1</v>
       </c>
       <c r="Q162" t="n">
-        <v>-6.386418013485318</v>
+        <v>35.63318870299522</v>
       </c>
     </row>
     <row r="163">
@@ -9926,25 +9728,25 @@
         <v>6</v>
       </c>
       <c r="K163" t="n">
-        <v>12.09432674237669</v>
+        <v>12.0939672988404</v>
       </c>
       <c r="L163" t="n">
         <v>26.5575104250525</v>
       </c>
       <c r="M163" t="n">
-        <v>9.502707810945383</v>
+        <v>10.05556289128236</v>
       </c>
       <c r="N163" t="n">
-        <v>13.38869754162123</v>
+        <v>25.08666927912393</v>
       </c>
       <c r="O163" t="n">
-        <v>11.4457026762833</v>
+        <v>17.57111608520314</v>
       </c>
       <c r="P163" t="b">
         <v>1</v>
       </c>
       <c r="Q163" t="n">
-        <v>-5.666965886134756</v>
+        <v>31.17131979439327</v>
       </c>
     </row>
     <row r="164">
@@ -9985,25 +9787,25 @@
         <v>6</v>
       </c>
       <c r="K164" t="n">
-        <v>12.31599521887282</v>
+        <v>12.30220165692974</v>
       </c>
       <c r="L164" t="n">
         <v>27.11369557085114</v>
       </c>
       <c r="M164" t="n">
-        <v>9.747179920199084</v>
+        <v>9.001199936508684</v>
       </c>
       <c r="N164" t="n">
-        <v>13.08301745600236</v>
+        <v>3.792145425414864</v>
       </c>
       <c r="O164" t="n">
-        <v>11.41509868810072</v>
+        <v>6.396672680961774</v>
       </c>
       <c r="P164" t="b">
         <v>1</v>
       </c>
       <c r="Q164" t="n">
-        <v>-7.892148420155198</v>
+        <v>-92.32188780808524</v>
       </c>
     </row>
     <row r="165">
@@ -10044,25 +9846,25 @@
         <v>6</v>
       </c>
       <c r="K165" t="n">
-        <v>12.5062115616939</v>
+        <v>12.50813670960662</v>
       </c>
       <c r="L165" t="n">
         <v>27.17255957488177</v>
       </c>
       <c r="M165" t="n">
-        <v>9.919536055839442</v>
+        <v>8.859202453554882</v>
       </c>
       <c r="N165" t="n">
-        <v>13.08301745600236</v>
+        <v>3.792145425414864</v>
       </c>
       <c r="O165" t="n">
-        <v>11.5012767559209</v>
+        <v>6.325673939484873</v>
       </c>
       <c r="P165" t="b">
         <v>1</v>
       </c>
       <c r="Q165" t="n">
-        <v>-8.737593461140358</v>
+        <v>-97.73603301824956</v>
       </c>
     </row>
     <row r="166">
@@ -10103,25 +9905,25 @@
         <v>6</v>
       </c>
       <c r="K166" t="n">
-        <v>13.12036788826173</v>
+        <v>13.12139488965561</v>
       </c>
       <c r="L166" t="n">
         <v>27.49149957593224</v>
       </c>
       <c r="M166" t="n">
-        <v>10.03982707763049</v>
+        <v>8.859202453554882</v>
       </c>
       <c r="N166" t="n">
-        <v>12.00715379503883</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="O166" t="n">
-        <v>11.02349043633466</v>
+        <v>5.582844451878379</v>
       </c>
       <c r="P166" t="b">
         <v>1</v>
       </c>
       <c r="Q166" t="n">
-        <v>-19.0219011304761</v>
+        <v>-135.0306372093323</v>
       </c>
     </row>
     <row r="167">
@@ -10162,25 +9964,25 @@
         <v>6</v>
       </c>
       <c r="K167" t="n">
-        <v>13.1463425367316</v>
+        <v>13.1377199395177</v>
       </c>
       <c r="L167" t="n">
         <v>27.50773554414463</v>
       </c>
       <c r="M167" t="n">
-        <v>10.03982707763049</v>
+        <v>8.859202453554882</v>
       </c>
       <c r="N167" t="n">
-        <v>12.00715379503883</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="O167" t="n">
-        <v>11.02349043633466</v>
+        <v>5.582844451878379</v>
       </c>
       <c r="P167" t="b">
         <v>1</v>
       </c>
       <c r="Q167" t="n">
-        <v>-19.25753111192241</v>
+        <v>-135.3230517661556</v>
       </c>
     </row>
     <row r="168">
@@ -10221,25 +10023,25 @@
         <v>6</v>
       </c>
       <c r="K168" t="n">
-        <v>13.18008131564125</v>
+        <v>13.18039755108718</v>
       </c>
       <c r="L168" t="n">
         <v>27.56406281162815</v>
       </c>
       <c r="M168" t="n">
-        <v>10.03982707763049</v>
+        <v>8.984742925862029</v>
       </c>
       <c r="N168" t="n">
-        <v>12.00715379503883</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="O168" t="n">
-        <v>11.02349043633466</v>
+        <v>5.645614688031952</v>
       </c>
       <c r="P168" t="b">
         <v>1</v>
       </c>
       <c r="Q168" t="n">
-        <v>-19.56359368896647</v>
+        <v>-133.4625772288019</v>
       </c>
     </row>
     <row r="169">
@@ -10280,25 +10082,25 @@
         <v>6</v>
       </c>
       <c r="K169" t="n">
-        <v>13.40114512882637</v>
+        <v>13.40216427255851</v>
       </c>
       <c r="L169" t="n">
         <v>27.68519049114493</v>
       </c>
       <c r="M169" t="n">
-        <v>10.10075936227274</v>
+        <v>8.988563827679902</v>
       </c>
       <c r="N169" t="n">
-        <v>12.00715379503883</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="O169" t="n">
-        <v>11.05395657865578</v>
+        <v>5.647525138940889</v>
       </c>
       <c r="P169" t="b">
         <v>1</v>
       </c>
       <c r="Q169" t="n">
-        <v>-21.23392229260965</v>
+        <v>-137.3103960201564</v>
       </c>
     </row>
     <row r="170">
@@ -10339,25 +10141,25 @@
         <v>6</v>
       </c>
       <c r="K170" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
       <c r="L170" t="n">
         <v>27.79521256732658</v>
       </c>
       <c r="M170" t="n">
-        <v>10.18523871563691</v>
+        <v>8.988563827679902</v>
       </c>
       <c r="N170" t="n">
-        <v>11.12071911562041</v>
+        <v>2.243417761691069</v>
       </c>
       <c r="O170" t="n">
-        <v>10.65297891562866</v>
+        <v>5.615990794685485</v>
       </c>
       <c r="P170" t="b">
         <v>1</v>
       </c>
       <c r="Q170" t="n">
-        <v>-26.88700682599543</v>
+        <v>-140.7002609379794</v>
       </c>
     </row>
     <row r="171">
@@ -10398,25 +10200,25 @@
         <v>6</v>
       </c>
       <c r="K171" t="n">
-        <v>13.51724608384559</v>
+        <v>13.51770449706086</v>
       </c>
       <c r="L171" t="n">
         <v>27.80479370484158</v>
       </c>
       <c r="M171" t="n">
-        <v>10.18523871563691</v>
+        <v>8.988563827679902</v>
       </c>
       <c r="N171" t="n">
-        <v>11.12071911562041</v>
+        <v>2.243417761691069</v>
       </c>
       <c r="O171" t="n">
-        <v>10.65297891562866</v>
+        <v>5.615990794685485</v>
       </c>
       <c r="P171" t="b">
         <v>1</v>
       </c>
       <c r="Q171" t="n">
-        <v>-26.88700682599543</v>
+        <v>-140.7002609379794</v>
       </c>
     </row>
     <row r="172">
@@ -10457,25 +10259,25 @@
         <v>6</v>
       </c>
       <c r="K172" t="n">
-        <v>13.45049177307704</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="L172" t="n">
         <v>28.10869932920667</v>
       </c>
       <c r="M172" t="n">
-        <v>10.3241301980949</v>
+        <v>8.809891251011997</v>
       </c>
       <c r="N172" t="n">
-        <v>10.85358927129134</v>
+        <v>2.208840509380332</v>
       </c>
       <c r="O172" t="n">
-        <v>10.58885973469312</v>
+        <v>5.509365880196165</v>
       </c>
       <c r="P172" t="b">
         <v>1</v>
       </c>
       <c r="Q172" t="n">
-        <v>-27.02493101318673</v>
+        <v>-143.7367123165402</v>
       </c>
     </row>
     <row r="173">
@@ -10516,25 +10318,25 @@
         <v>6</v>
       </c>
       <c r="K173" t="n">
-        <v>13.41663382802796</v>
+        <v>13.42834726587935</v>
       </c>
       <c r="L173" t="n">
         <v>28.1167578336159</v>
       </c>
       <c r="M173" t="n">
-        <v>10.3241301980949</v>
+        <v>8.809891251011997</v>
       </c>
       <c r="N173" t="n">
-        <v>10.85358927129134</v>
+        <v>2.208840509380332</v>
       </c>
       <c r="O173" t="n">
-        <v>10.58885973469312</v>
+        <v>5.509365880196165</v>
       </c>
       <c r="P173" t="b">
         <v>1</v>
       </c>
       <c r="Q173" t="n">
-        <v>-26.70518038944252</v>
+        <v>-143.7367123165402</v>
       </c>
     </row>
     <row r="174">
@@ -10575,25 +10377,25 @@
         <v>6</v>
       </c>
       <c r="K174" t="n">
-        <v>13.1360587715864</v>
+        <v>13.13596054003147</v>
       </c>
       <c r="L174" t="n">
         <v>28.26958022670045</v>
       </c>
       <c r="M174" t="n">
-        <v>10.72804752206529</v>
+        <v>8.809891251011997</v>
       </c>
       <c r="N174" t="n">
-        <v>9.881316214137952</v>
+        <v>2.178366503501772</v>
       </c>
       <c r="O174" t="n">
-        <v>10.30468186810162</v>
+        <v>5.494128877256885</v>
       </c>
       <c r="P174" t="b">
         <v>1</v>
       </c>
       <c r="Q174" t="n">
-        <v>-27.47660665051066</v>
+        <v>-139.0908701542875</v>
       </c>
     </row>
     <row r="175">
@@ -10634,25 +10436,25 @@
         <v>6</v>
       </c>
       <c r="K175" t="n">
-        <v>12.383252203665</v>
+        <v>12.3818195935645</v>
       </c>
       <c r="L175" t="n">
         <v>28.47322566290342</v>
       </c>
       <c r="M175" t="n">
-        <v>10.72804752206529</v>
+        <v>8.01349959414503</v>
       </c>
       <c r="N175" t="n">
-        <v>11.14758600080647</v>
+        <v>1.933592818035819</v>
       </c>
       <c r="O175" t="n">
-        <v>10.93781676143588</v>
+        <v>4.973546206090424</v>
       </c>
       <c r="P175" t="b">
         <v>1</v>
       </c>
       <c r="Q175" t="n">
-        <v>-13.21502703652324</v>
+        <v>-148.9535450259249</v>
       </c>
     </row>
     <row r="176">
@@ -10693,25 +10495,25 @@
         <v>6</v>
       </c>
       <c r="K176" t="n">
-        <v>12.32503009871696</v>
+        <v>12.34488939642437</v>
       </c>
       <c r="L176" t="n">
         <v>28.51606182167382</v>
       </c>
       <c r="M176" t="n">
-        <v>10.82821853712411</v>
+        <v>7.879726061462629</v>
       </c>
       <c r="N176" t="n">
-        <v>11.14758600080647</v>
+        <v>1.933592818035819</v>
       </c>
       <c r="O176" t="n">
-        <v>10.98790226896529</v>
+        <v>4.906659439749224</v>
       </c>
       <c r="P176" t="b">
         <v>1</v>
       </c>
       <c r="Q176" t="n">
-        <v>-12.16909103322033</v>
+        <v>-151.5945838102698</v>
       </c>
     </row>
     <row r="177">
@@ -10752,25 +10554,25 @@
         <v>6</v>
       </c>
       <c r="K177" t="n">
-        <v>11.8644104980694</v>
+        <v>11.86363453966294</v>
       </c>
       <c r="L177" t="n">
         <v>28.69477429651101</v>
       </c>
       <c r="M177" t="n">
-        <v>10.82821853712411</v>
+        <v>7.613353376700388</v>
       </c>
       <c r="N177" t="n">
-        <v>11.26473801004819</v>
+        <v>1.754995274249072</v>
       </c>
       <c r="O177" t="n">
-        <v>11.04647827358615</v>
+        <v>4.68417432547473</v>
       </c>
       <c r="P177" t="b">
         <v>1</v>
       </c>
       <c r="Q177" t="n">
-        <v>-7.404461442150789</v>
+        <v>-153.2705598752579</v>
       </c>
     </row>
     <row r="178">
@@ -10811,25 +10613,25 @@
         <v>6</v>
       </c>
       <c r="K178" t="n">
-        <v>11.66991607980337</v>
+        <v>11.66917292052748</v>
       </c>
       <c r="L178" t="n">
         <v>28.77621022108145</v>
       </c>
       <c r="M178" t="n">
-        <v>11.31153344108232</v>
+        <v>7.613353376700388</v>
       </c>
       <c r="N178" t="n">
-        <v>11.26473801004819</v>
+        <v>1.754995274249072</v>
       </c>
       <c r="O178" t="n">
-        <v>11.28813572556526</v>
+        <v>4.68417432547473</v>
       </c>
       <c r="P178" t="b">
         <v>1</v>
       </c>
       <c r="Q178" t="n">
-        <v>-3.382138233627519</v>
+        <v>-149.1190999674171</v>
       </c>
     </row>
     <row r="179">
@@ -10870,25 +10672,25 @@
         <v>6</v>
       </c>
       <c r="K179" t="n">
-        <v>11.4397626168475</v>
+        <v>11.44003729032269</v>
       </c>
       <c r="L179" t="n">
         <v>28.95302726951999</v>
       </c>
       <c r="M179" t="n">
-        <v>11.31153344108232</v>
+        <v>7.52583147660655</v>
       </c>
       <c r="N179" t="n">
-        <v>11.26473801004819</v>
+        <v>1.685429034276147</v>
       </c>
       <c r="O179" t="n">
-        <v>11.28813572556526</v>
+        <v>4.605630255441349</v>
       </c>
       <c r="P179" t="b">
         <v>1</v>
       </c>
       <c r="Q179" t="n">
-        <v>-1.343241213328383</v>
+        <v>-148.392438294559</v>
       </c>
     </row>
     <row r="180">
@@ -10929,25 +10731,25 @@
         <v>6</v>
       </c>
       <c r="K180" t="n">
-        <v>11.37121225770263</v>
+        <v>11.37095695966775</v>
       </c>
       <c r="L180" t="n">
         <v>29.00631685579318</v>
       </c>
       <c r="M180" t="n">
-        <v>11.3428515747395</v>
+        <v>7.52583147660655</v>
       </c>
       <c r="N180" t="n">
-        <v>11.9975006749236</v>
+        <v>1.550940467234431</v>
       </c>
       <c r="O180" t="n">
-        <v>11.67017612483155</v>
+        <v>4.538385971920491</v>
       </c>
       <c r="P180" t="b">
         <v>1</v>
       </c>
       <c r="Q180" t="n">
-        <v>2.561776822654738</v>
+        <v>-150.5506810134959</v>
       </c>
     </row>
     <row r="181">
@@ -10988,25 +10790,25 @@
         <v>6</v>
       </c>
       <c r="K181" t="n">
-        <v>11.08346970895239</v>
+        <v>11.0824964530113</v>
       </c>
       <c r="L181" t="n">
         <v>29.42662475403464</v>
       </c>
       <c r="M181" t="n">
-        <v>11.6068897425725</v>
+        <v>7.834451497123795</v>
       </c>
       <c r="N181" t="n">
-        <v>11.9975006749236</v>
+        <v>1.516284167734536</v>
       </c>
       <c r="O181" t="n">
-        <v>11.80219520874805</v>
+        <v>4.675367832429165</v>
       </c>
       <c r="P181" t="b">
         <v>1</v>
       </c>
       <c r="Q181" t="n">
-        <v>6.089761159541906</v>
+        <v>-137.0400971692789</v>
       </c>
     </row>
     <row r="182">
@@ -11047,25 +10849,25 @@
         <v>6</v>
       </c>
       <c r="K182" t="n">
-        <v>11.09012132545501</v>
+        <v>11.09009195586846</v>
       </c>
       <c r="L182" t="n">
         <v>29.46648376329098</v>
       </c>
       <c r="M182" t="n">
-        <v>11.6490487157816</v>
+        <v>7.878513743038085</v>
       </c>
       <c r="N182" t="n">
-        <v>15.04996711991609</v>
+        <v>1.516284167734536</v>
       </c>
       <c r="O182" t="n">
-        <v>13.34950791784885</v>
+        <v>4.69739895538631</v>
       </c>
       <c r="P182" t="b">
         <v>1</v>
       </c>
       <c r="Q182" t="n">
-        <v>16.92486798987505</v>
+        <v>-136.0900588005607</v>
       </c>
     </row>
     <row r="183">
@@ -11106,25 +10908,25 @@
         <v>6</v>
       </c>
       <c r="K183" t="n">
-        <v>11.1133397312677</v>
+        <v>11.11346172376633</v>
       </c>
       <c r="L183" t="n">
         <v>29.48481997939106</v>
       </c>
       <c r="M183" t="n">
-        <v>11.6490487157816</v>
+        <v>7.878513743038085</v>
       </c>
       <c r="N183" t="n">
-        <v>15.04996711991609</v>
+        <v>1.516284167734536</v>
       </c>
       <c r="O183" t="n">
-        <v>13.34950791784885</v>
+        <v>4.69739895538631</v>
       </c>
       <c r="P183" t="b">
         <v>1</v>
       </c>
       <c r="Q183" t="n">
-        <v>16.75094093611719</v>
+        <v>-136.5875632305616</v>
       </c>
     </row>
     <row r="184">
@@ -11165,25 +10967,25 @@
         <v>6</v>
       </c>
       <c r="K184" t="n">
-        <v>11.38285727695747</v>
+        <v>11.38295853545234</v>
       </c>
       <c r="L184" t="n">
         <v>29.88574658082181</v>
       </c>
       <c r="M184" t="n">
-        <v>12.28759492419801</v>
+        <v>7.996384831667157</v>
       </c>
       <c r="N184" t="n">
-        <v>15.04996711991609</v>
+        <v>1.570954752442219</v>
       </c>
       <c r="O184" t="n">
-        <v>13.66878102205705</v>
+        <v>4.783669792054688</v>
       </c>
       <c r="P184" t="b">
         <v>1</v>
       </c>
       <c r="Q184" t="n">
-        <v>16.72368400233224</v>
+        <v>-137.9545209069105</v>
       </c>
     </row>
     <row r="185">
@@ -11224,25 +11026,25 @@
         <v>6</v>
       </c>
       <c r="K185" t="n">
-        <v>11.40930901230741</v>
+        <v>11.40906398075885</v>
       </c>
       <c r="L185" t="n">
         <v>29.94828884159397</v>
       </c>
       <c r="M185" t="n">
-        <v>12.28759492419801</v>
+        <v>7.996384831667157</v>
       </c>
       <c r="N185" t="n">
-        <v>18.76213980838786</v>
+        <v>1.570954752442219</v>
       </c>
       <c r="O185" t="n">
-        <v>15.52486736629294</v>
+        <v>4.783669792054688</v>
       </c>
       <c r="P185" t="b">
         <v>1</v>
       </c>
       <c r="Q185" t="n">
-        <v>26.50945903036239</v>
+        <v>-138.5002409595336</v>
       </c>
     </row>
     <row r="186">
@@ -11283,25 +11085,25 @@
         <v>7</v>
       </c>
       <c r="K186" t="n">
-        <v>11.63847912745985</v>
+        <v>11.63801176927609</v>
       </c>
       <c r="L186" t="n">
         <v>30.26514846298791</v>
       </c>
       <c r="M186" t="n">
-        <v>12.73187879407693</v>
+        <v>8.215642482556708</v>
       </c>
       <c r="N186" t="n">
-        <v>19.80017486787884</v>
+        <v>1.592462013330594</v>
       </c>
       <c r="O186" t="n">
-        <v>16.26602683097789</v>
+        <v>4.904052247943651</v>
       </c>
       <c r="P186" t="b">
         <v>1</v>
       </c>
       <c r="Q186" t="n">
-        <v>28.44915818474545</v>
+        <v>-137.3141879586641</v>
       </c>
     </row>
     <row r="187">
@@ -11342,25 +11144,25 @@
         <v>7</v>
       </c>
       <c r="K187" t="n">
-        <v>12.23669714585852</v>
+        <v>12.23561229550869</v>
       </c>
       <c r="L187" t="n">
         <v>30.76748646817272</v>
       </c>
       <c r="M187" t="n">
-        <v>12.73729214372356</v>
+        <v>8.661114516403142</v>
       </c>
       <c r="N187" t="n">
-        <v>32.70898051855441</v>
+        <v>1.565395665479873</v>
       </c>
       <c r="O187" t="n">
-        <v>22.72313633113899</v>
+        <v>5.113255090941507</v>
       </c>
       <c r="P187" t="b">
         <v>1</v>
       </c>
       <c r="Q187" t="n">
-        <v>46.14873155036358</v>
+        <v>-139.2920376138663</v>
       </c>
     </row>
     <row r="188">
@@ -11401,25 +11203,25 @@
         <v>7</v>
       </c>
       <c r="K188" t="n">
-        <v>12.32498885385217</v>
+        <v>12.32493800141896</v>
       </c>
       <c r="L188" t="n">
         <v>30.7910256566159</v>
       </c>
       <c r="M188" t="n">
-        <v>12.73729214372356</v>
+        <v>8.661114516403142</v>
       </c>
       <c r="N188" t="n">
-        <v>32.70898051855441</v>
+        <v>1.565395665479873</v>
       </c>
       <c r="O188" t="n">
-        <v>22.72313633113899</v>
+        <v>5.113255090941507</v>
       </c>
       <c r="P188" t="b">
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>45.76017731776562</v>
+        <v>-141.0389816704716</v>
       </c>
     </row>
     <row r="189">
@@ -11460,25 +11262,25 @@
         <v>7</v>
       </c>
       <c r="K189" t="n">
-        <v>12.6846002976039</v>
+        <v>12.68439321587084</v>
       </c>
       <c r="L189" t="n">
         <v>30.99086177749428</v>
       </c>
       <c r="M189" t="n">
-        <v>12.61379930677621</v>
+        <v>8.957982002673143</v>
       </c>
       <c r="N189" t="n">
-        <v>31.85520146279512</v>
+        <v>1.565395665479873</v>
       </c>
       <c r="O189" t="n">
-        <v>22.23450038478567</v>
+        <v>5.261688834076508</v>
       </c>
       <c r="P189" t="b">
         <v>1</v>
       </c>
       <c r="Q189" t="n">
-        <v>42.95081932093447</v>
+        <v>-141.0707591395816</v>
       </c>
     </row>
     <row r="190">
@@ -11519,25 +11321,25 @@
         <v>7</v>
       </c>
       <c r="K190" t="n">
-        <v>13.02992558520946</v>
+        <v>13.02958147828541</v>
       </c>
       <c r="L190" t="n">
         <v>31.21231008872709</v>
       </c>
       <c r="M190" t="n">
-        <v>12.48481118538775</v>
+        <v>9.118840462178738</v>
       </c>
       <c r="N190" t="n">
-        <v>28.60411152728559</v>
+        <v>1.419913546667344</v>
       </c>
       <c r="O190" t="n">
-        <v>20.54446135633667</v>
+        <v>5.269377004423041</v>
       </c>
       <c r="P190" t="b">
         <v>1</v>
       </c>
       <c r="Q190" t="n">
-        <v>36.57694227553672</v>
+        <v>-147.2698663874033</v>
       </c>
     </row>
     <row r="191">
@@ -11578,25 +11380,25 @@
         <v>7</v>
       </c>
       <c r="K191" t="n">
-        <v>13.11080079318839</v>
+        <v>13.10942074896131</v>
       </c>
       <c r="L191" t="n">
         <v>31.27059049972096</v>
       </c>
       <c r="M191" t="n">
-        <v>12.48481118538775</v>
+        <v>9.184142659321292</v>
       </c>
       <c r="N191" t="n">
-        <v>28.60411152728559</v>
+        <v>1.419913546667344</v>
       </c>
       <c r="O191" t="n">
-        <v>20.54446135633667</v>
+        <v>5.302028102994318</v>
       </c>
       <c r="P191" t="b">
         <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>36.18328285280382</v>
+        <v>-147.2529472553676</v>
       </c>
     </row>
     <row r="192">
@@ -11637,25 +11439,25 @@
         <v>7</v>
       </c>
       <c r="K192" t="n">
-        <v>13.23499422520247</v>
+        <v>13.21905420441579</v>
       </c>
       <c r="L192" t="n">
         <v>31.33692897489462</v>
       </c>
       <c r="M192" t="n">
-        <v>12.17667309377143</v>
+        <v>9.184142659321292</v>
       </c>
       <c r="N192" t="n">
-        <v>28.60411152728559</v>
+        <v>1.418340009755992</v>
       </c>
       <c r="O192" t="n">
-        <v>20.39039231052851</v>
+        <v>5.301241334538642</v>
       </c>
       <c r="P192" t="b">
         <v>1</v>
       </c>
       <c r="Q192" t="n">
-        <v>35.09200792390532</v>
+        <v>-149.3577139808939</v>
       </c>
     </row>
     <row r="193">
@@ -11696,25 +11498,25 @@
         <v>7</v>
       </c>
       <c r="K193" t="n">
-        <v>13.38869754162123</v>
+        <v>13.41609389853743</v>
       </c>
       <c r="L193" t="n">
         <v>31.42099787006858</v>
       </c>
       <c r="M193" t="n">
-        <v>12.17667309377143</v>
+        <v>9.503947719470569</v>
       </c>
       <c r="N193" t="n">
-        <v>28.60411152728559</v>
+        <v>1.430984911351356</v>
       </c>
       <c r="O193" t="n">
-        <v>20.39039231052851</v>
+        <v>5.467466315410962</v>
       </c>
       <c r="P193" t="b">
         <v>1</v>
       </c>
       <c r="Q193" t="n">
-        <v>34.33820527961095</v>
+        <v>-145.3804582338614</v>
       </c>
     </row>
     <row r="194">
@@ -11755,25 +11557,25 @@
         <v>7</v>
       </c>
       <c r="K194" t="n">
-        <v>13.84081620532295</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="L194" t="n">
         <v>31.74421893810658</v>
       </c>
       <c r="M194" t="n">
-        <v>12.09432674237669</v>
+        <v>9.601021663415642</v>
       </c>
       <c r="N194" t="n">
-        <v>24.15594055581073</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="O194" t="n">
-        <v>18.12513364909371</v>
+        <v>5.502515695896438</v>
       </c>
       <c r="P194" t="b">
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>23.63743918646901</v>
+        <v>-151.8275493070144</v>
       </c>
     </row>
     <row r="195">
@@ -11814,25 +11616,25 @@
         <v>7</v>
       </c>
       <c r="K195" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="L195" t="n">
         <v>31.76842246568006</v>
       </c>
       <c r="M195" t="n">
-        <v>12.09432674237669</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="N195" t="n">
-        <v>24.15594055581073</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="O195" t="n">
-        <v>18.12513364909371</v>
+        <v>5.535545122816441</v>
       </c>
       <c r="P195" t="b">
         <v>1</v>
       </c>
       <c r="Q195" t="n">
-        <v>23.55844089327018</v>
+        <v>-150.3249475845579</v>
       </c>
     </row>
     <row r="196">
@@ -11873,25 +11675,25 @@
         <v>7</v>
       </c>
       <c r="K196" t="n">
-        <v>13.85513475154574</v>
+        <v>13.85685042720981</v>
       </c>
       <c r="L196" t="n">
         <v>31.77337891873379</v>
       </c>
       <c r="M196" t="n">
-        <v>12.09432674237669</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="N196" t="n">
-        <v>24.15594055581073</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="O196" t="n">
-        <v>18.12513364909371</v>
+        <v>5.535545122816441</v>
       </c>
       <c r="P196" t="b">
         <v>1</v>
       </c>
       <c r="Q196" t="n">
-        <v>23.55844089327018</v>
+        <v>-150.3249475845579</v>
       </c>
     </row>
     <row r="197">
@@ -11932,25 +11734,25 @@
         <v>7</v>
       </c>
       <c r="K197" t="n">
-        <v>13.89603621482746</v>
+        <v>13.90173162460115</v>
       </c>
       <c r="L197" t="n">
         <v>31.85011850618602</v>
       </c>
       <c r="M197" t="n">
-        <v>12.31599521887282</v>
+        <v>9.667080517255647</v>
       </c>
       <c r="N197" t="n">
-        <v>3.785458746171327</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="O197" t="n">
-        <v>8.050726982522074</v>
+        <v>5.535545122816441</v>
       </c>
       <c r="P197" t="b">
         <v>1</v>
       </c>
       <c r="Q197" t="n">
-        <v>-72.60598011826025</v>
+        <v>-151.1357294749693</v>
       </c>
     </row>
     <row r="198">
@@ -11991,25 +11793,25 @@
         <v>7</v>
       </c>
       <c r="K198" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
       <c r="L198" t="n">
         <v>32.27137697662853</v>
       </c>
       <c r="M198" t="n">
-        <v>12.5062115616939</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="N198" t="n">
-        <v>3.785458746171327</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="O198" t="n">
-        <v>8.145835153932614</v>
+        <v>5.644333672833427</v>
       </c>
       <c r="P198" t="b">
         <v>1</v>
       </c>
       <c r="Q198" t="n">
-        <v>-60.60989706729081</v>
+        <v>-131.9065598076893</v>
       </c>
     </row>
     <row r="199">
@@ -12050,25 +11852,25 @@
         <v>7</v>
       </c>
       <c r="K199" t="n">
-        <v>13.08301745600236</v>
+        <v>13.08958004473499</v>
       </c>
       <c r="L199" t="n">
         <v>32.27291866188108</v>
       </c>
       <c r="M199" t="n">
-        <v>12.5062115616939</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="N199" t="n">
-        <v>3.785458746171327</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="O199" t="n">
-        <v>8.145835153932614</v>
+        <v>5.644333672833427</v>
       </c>
       <c r="P199" t="b">
         <v>1</v>
       </c>
       <c r="Q199" t="n">
-        <v>-60.60989706729081</v>
+        <v>-131.9065598076893</v>
       </c>
     </row>
     <row r="200">
@@ -12109,25 +11911,25 @@
         <v>7</v>
       </c>
       <c r="K200" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
       <c r="L200" t="n">
         <v>32.35809764522976</v>
       </c>
       <c r="M200" t="n">
-        <v>13.12036788826173</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="N200" t="n">
-        <v>3.785458746171327</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="O200" t="n">
-        <v>8.452913317216527</v>
+        <v>5.644333672833427</v>
       </c>
       <c r="P200" t="b">
         <v>1</v>
       </c>
       <c r="Q200" t="n">
-        <v>-51.34948846877758</v>
+        <v>-126.5948362292407</v>
       </c>
     </row>
     <row r="201">
@@ -12168,25 +11970,25 @@
         <v>7</v>
       </c>
       <c r="K201" t="n">
-        <v>12.79344106631639</v>
+        <v>12.78976864218879</v>
       </c>
       <c r="L201" t="n">
         <v>32.35843653122089</v>
       </c>
       <c r="M201" t="n">
-        <v>13.12036788826173</v>
+        <v>9.920481651612979</v>
       </c>
       <c r="N201" t="n">
-        <v>3.785458746171327</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="O201" t="n">
-        <v>8.452913317216527</v>
+        <v>5.644333672833427</v>
       </c>
       <c r="P201" t="b">
         <v>1</v>
       </c>
       <c r="Q201" t="n">
-        <v>-51.34948846877758</v>
+        <v>-126.5948362292407</v>
       </c>
     </row>
     <row r="202">
@@ -12227,25 +12029,25 @@
         <v>7</v>
       </c>
       <c r="K202" t="n">
-        <v>12.00715379503883</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="L202" t="n">
         <v>32.62410742688635</v>
       </c>
       <c r="M202" t="n">
-        <v>13.18008131564125</v>
+        <v>10.04873175068141</v>
       </c>
       <c r="N202" t="n">
-        <v>2.304981288314705</v>
+        <v>1.474906345155731</v>
       </c>
       <c r="O202" t="n">
-        <v>7.742531301977978</v>
+        <v>5.761819047918572</v>
       </c>
       <c r="P202" t="b">
         <v>1</v>
       </c>
       <c r="Q202" t="n">
-        <v>-55.08046821807966</v>
+        <v>-108.6745430145946</v>
       </c>
     </row>
     <row r="203">
@@ -12286,25 +12088,25 @@
         <v>7</v>
       </c>
       <c r="K203" t="n">
-        <v>11.12071911562041</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="L203" t="n">
         <v>32.90724088974186</v>
       </c>
       <c r="M203" t="n">
-        <v>13.51724608384559</v>
+        <v>10.32652469704417</v>
       </c>
       <c r="N203" t="n">
-        <v>2.242626634472161</v>
+        <v>1.452702989955006</v>
       </c>
       <c r="O203" t="n">
-        <v>7.879936359158876</v>
+        <v>5.889613843499587</v>
       </c>
       <c r="P203" t="b">
         <v>1</v>
       </c>
       <c r="Q203" t="n">
-        <v>-41.12701687869298</v>
+        <v>-92.79470709770375</v>
       </c>
     </row>
     <row r="204">
@@ -12345,25 +12147,25 @@
         <v>7</v>
       </c>
       <c r="K204" t="n">
-        <v>10.85358927129134</v>
+        <v>10.84914955146178</v>
       </c>
       <c r="L204" t="n">
         <v>33.17330593180686</v>
       </c>
       <c r="M204" t="n">
-        <v>13.41663382802796</v>
+        <v>10.32652469704417</v>
       </c>
       <c r="N204" t="n">
-        <v>2.177717576724394</v>
+        <v>1.45809868005846</v>
       </c>
       <c r="O204" t="n">
-        <v>7.797175702376178</v>
+        <v>5.892311688551314</v>
       </c>
       <c r="P204" t="b">
         <v>1</v>
       </c>
       <c r="Q204" t="n">
-        <v>-39.19898288278569</v>
+        <v>-84.12382312601585</v>
       </c>
     </row>
     <row r="205">
@@ -12404,25 +12206,25 @@
         <v>7</v>
       </c>
       <c r="K205" t="n">
-        <v>9.881316214137952</v>
+        <v>9.795415074047549</v>
       </c>
       <c r="L205" t="n">
         <v>33.32651757975102</v>
       </c>
       <c r="M205" t="n">
-        <v>13.1360587715864</v>
+        <v>10.73329757505697</v>
       </c>
       <c r="N205" t="n">
-        <v>2.177717576724394</v>
+        <v>1.420974824777689</v>
       </c>
       <c r="O205" t="n">
-        <v>7.656888174155395</v>
+        <v>6.077136199917328</v>
       </c>
       <c r="P205" t="b">
         <v>1</v>
       </c>
       <c r="Q205" t="n">
-        <v>-29.05133246546239</v>
+        <v>-61.18472174740468</v>
       </c>
     </row>
     <row r="206">
@@ -12463,25 +12265,25 @@
         <v>7</v>
       </c>
       <c r="K206" t="n">
-        <v>11.14758600080647</v>
+        <v>11.14361891424003</v>
       </c>
       <c r="L206" t="n">
         <v>33.60224343578643</v>
       </c>
       <c r="M206" t="n">
-        <v>12.32503009871696</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="N206" t="n">
-        <v>1.931966466609836</v>
+        <v>1.324786460954448</v>
       </c>
       <c r="O206" t="n">
-        <v>7.128498282663398</v>
+        <v>6.078420185823534</v>
       </c>
       <c r="P206" t="b">
         <v>1</v>
       </c>
       <c r="Q206" t="n">
-        <v>-56.38056654818237</v>
+        <v>-83.33084211963275</v>
       </c>
     </row>
     <row r="207">
@@ -12522,25 +12324,25 @@
         <v>7</v>
       </c>
       <c r="K207" t="n">
-        <v>11.26473801004819</v>
+        <v>11.2617197355591</v>
       </c>
       <c r="L207" t="n">
         <v>33.69350658355038</v>
       </c>
       <c r="M207" t="n">
-        <v>11.8644104980694</v>
+        <v>10.83205391069262</v>
       </c>
       <c r="N207" t="n">
-        <v>1.753667849845577</v>
+        <v>1.292365108441281</v>
       </c>
       <c r="O207" t="n">
-        <v>6.80903917395749</v>
+        <v>6.062209509566951</v>
       </c>
       <c r="P207" t="b">
         <v>1</v>
       </c>
       <c r="Q207" t="n">
-        <v>-65.43799679009632</v>
+        <v>-85.76922684355675</v>
       </c>
     </row>
     <row r="208">
@@ -12581,25 +12383,25 @@
         <v>7</v>
       </c>
       <c r="K208" t="n">
-        <v>11.9975006749236</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="L208" t="n">
         <v>34.23263713652924</v>
       </c>
       <c r="M208" t="n">
-        <v>11.08346970895239</v>
+        <v>11.56684451772449</v>
       </c>
       <c r="N208" t="n">
-        <v>1.529696341903444</v>
+        <v>1.314231504832959</v>
       </c>
       <c r="O208" t="n">
-        <v>6.306583025427919</v>
+        <v>6.440538011278723</v>
       </c>
       <c r="P208" t="b">
         <v>1</v>
       </c>
       <c r="Q208" t="n">
-        <v>-90.23773454737861</v>
+        <v>-86.25364045246361</v>
       </c>
     </row>
     <row r="209">
@@ -12640,25 +12442,25 @@
         <v>7</v>
       </c>
       <c r="K209" t="n">
-        <v>15.04996711991609</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="L209" t="n">
         <v>34.70008382296992</v>
       </c>
       <c r="M209" t="n">
-        <v>11.38285727695747</v>
+        <v>11.65030216584749</v>
       </c>
       <c r="N209" t="n">
-        <v>1.57526681032956</v>
+        <v>1.494545066258282</v>
       </c>
       <c r="O209" t="n">
-        <v>6.479062043643514</v>
+        <v>6.572423616052887</v>
       </c>
       <c r="P209" t="b">
         <v>1</v>
       </c>
       <c r="Q209" t="n">
-        <v>-132.2862015911906</v>
+        <v>-128.9048174916805</v>
       </c>
     </row>
     <row r="210">
@@ -12699,25 +12501,25 @@
         <v>7</v>
       </c>
       <c r="K210" t="n">
-        <v>15.04996711991609</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="L210" t="n">
         <v>34.74885758270663</v>
       </c>
       <c r="M210" t="n">
-        <v>11.38285727695747</v>
+        <v>12.28927385385947</v>
       </c>
       <c r="N210" t="n">
-        <v>1.57526681032956</v>
+        <v>1.494545066258282</v>
       </c>
       <c r="O210" t="n">
-        <v>6.479062043643514</v>
+        <v>6.891909460058875</v>
       </c>
       <c r="P210" t="b">
         <v>1</v>
       </c>
       <c r="Q210" t="n">
-        <v>-132.2862015911906</v>
+        <v>-118.2935566738779</v>
       </c>
     </row>
     <row r="211">
@@ -12758,25 +12560,25 @@
         <v>7</v>
       </c>
       <c r="K211" t="n">
-        <v>18.76213980838786</v>
+        <v>18.75529113087354</v>
       </c>
       <c r="L211" t="n">
         <v>35.10775085579925</v>
       </c>
       <c r="M211" t="n">
-        <v>11.63847912745985</v>
+        <v>12.56367312450933</v>
       </c>
       <c r="N211" t="n">
-        <v>1.565429483712482</v>
+        <v>8.876632772914137</v>
       </c>
       <c r="O211" t="n">
-        <v>6.601954305586165</v>
+        <v>10.72015294871174</v>
       </c>
       <c r="P211" t="b">
         <v>1</v>
       </c>
       <c r="Q211" t="n">
-        <v>-184.1906947540139</v>
+        <v>-74.95357781371399</v>
       </c>
     </row>
     <row r="212">
@@ -12817,25 +12619,25 @@
         <v>7</v>
       </c>
       <c r="K212" t="n">
-        <v>19.80017486787884</v>
+        <v>19.78860372735059</v>
       </c>
       <c r="L212" t="n">
         <v>35.28226033578176</v>
       </c>
       <c r="M212" t="n">
-        <v>11.63847912745985</v>
+        <v>12.73286697894567</v>
       </c>
       <c r="N212" t="n">
-        <v>1.593142183310019</v>
+        <v>8.876632772914137</v>
       </c>
       <c r="O212" t="n">
-        <v>6.615810655384934</v>
+        <v>10.8047498759299</v>
       </c>
       <c r="P212" t="b">
         <v>1</v>
       </c>
       <c r="Q212" t="n">
-        <v>-199.285694516703</v>
+        <v>-83.14726351448745</v>
       </c>
     </row>
     <row r="213">
@@ -12876,26 +12678,20 @@
         <v>7</v>
       </c>
       <c r="K213" t="n">
-        <v>25.75018995464015</v>
+        <v>25.70526768557929</v>
       </c>
       <c r="L213" t="n">
         <v>35.46727829514772</v>
       </c>
       <c r="M213" t="n">
-        <v>11.63847912745985</v>
-      </c>
-      <c r="N213" t="n">
-        <v>1.610697573322888</v>
-      </c>
-      <c r="O213" t="n">
-        <v>6.624588350391369</v>
-      </c>
+        <v>12.90108600673018</v>
+      </c>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
       <c r="P213" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>-288.7062650937227</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -12935,26 +12731,20 @@
         <v>7</v>
       </c>
       <c r="K214" t="n">
-        <v>29.51809009266479</v>
+        <v>29.46584073043611</v>
       </c>
       <c r="L214" t="n">
         <v>35.5323589695709</v>
       </c>
       <c r="M214" t="n">
-        <v>12.23669714585852</v>
-      </c>
-      <c r="N214" t="n">
-        <v>1.610697573322888</v>
-      </c>
-      <c r="O214" t="n">
-        <v>6.923697359590705</v>
-      </c>
+        <v>12.90108600673018</v>
+      </c>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>-326.3342049718036</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -12994,26 +12784,20 @@
         <v>7</v>
       </c>
       <c r="K215" t="n">
-        <v>32.70898051855441</v>
+        <v>32.72010281853873</v>
       </c>
       <c r="L215" t="n">
         <v>35.81499432032926</v>
       </c>
       <c r="M215" t="n">
-        <v>12.32498885385217</v>
-      </c>
-      <c r="N215" t="n">
-        <v>1.564238403151555</v>
-      </c>
-      <c r="O215" t="n">
-        <v>6.94461362850186</v>
-      </c>
+        <v>12.73686903582316</v>
+      </c>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr"/>
       <c r="P215" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>-370.9978447801799</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -13053,26 +12837,20 @@
         <v>7</v>
       </c>
       <c r="K216" t="n">
-        <v>32.70898051855441</v>
+        <v>32.72010281853873</v>
       </c>
       <c r="L216" t="n">
         <v>35.82435611903663</v>
       </c>
       <c r="M216" t="n">
-        <v>12.32498885385217</v>
-      </c>
-      <c r="N216" t="n">
-        <v>1.564238403151555</v>
-      </c>
-      <c r="O216" t="n">
-        <v>6.94461362850186</v>
-      </c>
+        <v>12.73686903582316</v>
+      </c>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
       <c r="P216" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>-370.9978447801799</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -13112,26 +12890,20 @@
         <v>7</v>
       </c>
       <c r="K217" t="n">
-        <v>32.70898051855441</v>
+        <v>32.72010281853873</v>
       </c>
       <c r="L217" t="n">
         <v>35.87877945237903</v>
       </c>
       <c r="M217" t="n">
-        <v>12.32498885385217</v>
-      </c>
-      <c r="N217" t="n">
-        <v>1.564238403151555</v>
-      </c>
-      <c r="O217" t="n">
-        <v>6.94461362850186</v>
-      </c>
+        <v>12.73686903582316</v>
+      </c>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
       <c r="P217" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>-370.9978447801799</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -13171,26 +12943,20 @@
         <v>7</v>
       </c>
       <c r="K218" t="n">
-        <v>31.85520146279512</v>
+        <v>31.86592787966785</v>
       </c>
       <c r="L218" t="n">
         <v>35.92229394470053</v>
       </c>
       <c r="M218" t="n">
-        <v>12.6846002976039</v>
-      </c>
-      <c r="N218" t="n">
-        <v>1.564238403151555</v>
-      </c>
-      <c r="O218" t="n">
-        <v>7.124419350377726</v>
-      </c>
+        <v>12.61285613536885</v>
+      </c>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
       <c r="P218" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>-347.1269853185469</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -13230,26 +12996,20 @@
         <v>7</v>
       </c>
       <c r="K219" t="n">
-        <v>31.85520146279512</v>
+        <v>31.86592787966785</v>
       </c>
       <c r="L219" t="n">
         <v>35.97553704907125</v>
       </c>
       <c r="M219" t="n">
-        <v>12.6846002976039</v>
-      </c>
-      <c r="N219" t="n">
-        <v>1.564238403151555</v>
-      </c>
-      <c r="O219" t="n">
-        <v>7.124419350377726</v>
-      </c>
+        <v>12.61285613536885</v>
+      </c>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
       <c r="P219" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q219" t="n">
-        <v>-347.1269853185469</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -13289,26 +13049,20 @@
         <v>7</v>
       </c>
       <c r="K220" t="n">
-        <v>28.60411152728559</v>
+        <v>27.77808184280534</v>
       </c>
       <c r="L220" t="n">
         <v>36.39265426083555</v>
       </c>
       <c r="M220" t="n">
-        <v>13.38869754162123</v>
-      </c>
-      <c r="N220" t="n">
-        <v>1.418578208833067</v>
-      </c>
-      <c r="O220" t="n">
-        <v>7.403637875227147</v>
-      </c>
+        <v>12.17615535638471</v>
+      </c>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
       <c r="P220" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q220" t="n">
-        <v>-286.3521151270247</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -13348,26 +13102,20 @@
         <v>7</v>
       </c>
       <c r="K221" t="n">
-        <v>25.06879742216805</v>
+        <v>25.08666927912393</v>
       </c>
       <c r="L221" t="n">
         <v>36.54234734290672</v>
       </c>
       <c r="M221" t="n">
-        <v>13.38869754162123</v>
-      </c>
-      <c r="N221" t="n">
-        <v>1.431146441684962</v>
-      </c>
-      <c r="O221" t="n">
-        <v>7.409921991653095</v>
-      </c>
+        <v>12.0939672988404</v>
+      </c>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
       <c r="P221" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q221" t="n">
-        <v>-238.3139181546957</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -13407,26 +13155,20 @@
         <v>19</v>
       </c>
       <c r="K222" t="n">
-        <v>24.15594055581073</v>
+        <v>23.63636222913874</v>
       </c>
       <c r="L222" t="n">
         <v>36.61298137721217</v>
       </c>
       <c r="M222" t="n">
-        <v>13.84081620532295</v>
-      </c>
-      <c r="N222" t="n">
-        <v>1.431146441684962</v>
-      </c>
-      <c r="O222" t="n">
-        <v>7.635981323503957</v>
-      </c>
+        <v>12.0939672988404</v>
+      </c>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
       <c r="P222" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q222" t="n">
-        <v>-216.343630666794</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -13466,26 +13208,20 @@
         <v>19</v>
       </c>
       <c r="K223" t="n">
-        <v>3.785458746171327</v>
+        <v>3.792145425414864</v>
       </c>
       <c r="L223" t="n">
         <v>37.05711655241912</v>
       </c>
       <c r="M223" t="n">
-        <v>13.89603621482746</v>
-      </c>
-      <c r="N223" t="n">
-        <v>1.371697587884001</v>
-      </c>
-      <c r="O223" t="n">
-        <v>7.633866901355732</v>
-      </c>
+        <v>12.30220165692974</v>
+      </c>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
       <c r="P223" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q223" t="n">
-        <v>50.41230355353653</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -13525,26 +13261,20 @@
         <v>19</v>
       </c>
       <c r="K224" t="n">
-        <v>3.785458746171327</v>
+        <v>3.792145425414864</v>
       </c>
       <c r="L224" t="n">
         <v>37.0802416852183</v>
       </c>
       <c r="M224" t="n">
-        <v>13.08301745600236</v>
-      </c>
-      <c r="N224" t="n">
-        <v>1.371697587884001</v>
-      </c>
-      <c r="O224" t="n">
-        <v>7.227357521943181</v>
-      </c>
+        <v>12.30220165692974</v>
+      </c>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
       <c r="P224" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q224" t="n">
-        <v>47.62319790216285</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -13584,26 +13314,20 @@
         <v>19</v>
       </c>
       <c r="K225" t="n">
-        <v>2.304981288314705</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="L225" t="n">
         <v>37.63937154478135</v>
       </c>
       <c r="M225" t="n">
-        <v>12.00715379503883</v>
-      </c>
-      <c r="N225" t="n">
-        <v>1.473969960651437</v>
-      </c>
-      <c r="O225" t="n">
-        <v>6.740561877845133</v>
-      </c>
+        <v>13.40216427255851</v>
+      </c>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
       <c r="P225" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>65.8043152768805</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -13643,26 +13367,20 @@
         <v>19</v>
       </c>
       <c r="K226" t="n">
-        <v>2.304981288314705</v>
+        <v>2.306486450201875</v>
       </c>
       <c r="L226" t="n">
         <v>37.64225937895285</v>
       </c>
       <c r="M226" t="n">
-        <v>12.00715379503883</v>
-      </c>
-      <c r="N226" t="n">
-        <v>1.473969960651437</v>
-      </c>
-      <c r="O226" t="n">
-        <v>6.740561877845133</v>
-      </c>
+        <v>13.40216427255851</v>
+      </c>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
       <c r="P226" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q226" t="n">
-        <v>65.8043152768805</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -13702,26 +13420,20 @@
         <v>19</v>
       </c>
       <c r="K227" t="n">
-        <v>2.242626634472161</v>
+        <v>2.243417761691069</v>
       </c>
       <c r="L227" t="n">
         <v>37.74031479846446</v>
       </c>
       <c r="M227" t="n">
-        <v>12.00715379503883</v>
-      </c>
-      <c r="N227" t="n">
-        <v>1.473969960651437</v>
-      </c>
-      <c r="O227" t="n">
-        <v>6.740561877845133</v>
-      </c>
+        <v>13.51770449706086</v>
+      </c>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q227" t="n">
-        <v>66.72938139113857</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -13761,26 +13473,20 @@
         <v>19</v>
       </c>
       <c r="K228" t="n">
-        <v>2.242626634472161</v>
+        <v>2.243417761691069</v>
       </c>
       <c r="L228" t="n">
         <v>37.79521475577916</v>
       </c>
       <c r="M228" t="n">
-        <v>11.12071911562041</v>
-      </c>
-      <c r="N228" t="n">
-        <v>1.473969960651437</v>
-      </c>
-      <c r="O228" t="n">
-        <v>6.297344538135925</v>
-      </c>
+        <v>13.51770449706086</v>
+      </c>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
       <c r="P228" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q228" t="n">
-        <v>64.38774119962633</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -13820,26 +13526,20 @@
         <v>19</v>
       </c>
       <c r="K229" t="n">
-        <v>2.208926235719771</v>
+        <v>2.208840509380332</v>
       </c>
       <c r="L229" t="n">
         <v>38.06752660594819</v>
       </c>
       <c r="M229" t="n">
-        <v>10.85358927129134</v>
-      </c>
-      <c r="N229" t="n">
-        <v>1.455108032295628</v>
-      </c>
-      <c r="O229" t="n">
-        <v>6.154348651793485</v>
-      </c>
+        <v>13.42834726587935</v>
+      </c>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
       <c r="P229" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q229" t="n">
-        <v>64.10787947354832</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -13879,26 +13579,20 @@
         <v>19</v>
       </c>
       <c r="K230" t="n">
-        <v>2.208926235719771</v>
+        <v>2.208840509380332</v>
       </c>
       <c r="L230" t="n">
         <v>38.08902081888078</v>
       </c>
       <c r="M230" t="n">
-        <v>10.85358927129134</v>
-      </c>
-      <c r="N230" t="n">
-        <v>1.455108032295628</v>
-      </c>
-      <c r="O230" t="n">
-        <v>6.154348651793485</v>
-      </c>
+        <v>13.42834726587935</v>
+      </c>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
       <c r="P230" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q230" t="n">
-        <v>64.10787947354832</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -13938,26 +13632,20 @@
         <v>19</v>
       </c>
       <c r="K231" t="n">
-        <v>2.177717576724394</v>
+        <v>2.178366503501772</v>
       </c>
       <c r="L231" t="n">
         <v>38.24711285351321</v>
       </c>
       <c r="M231" t="n">
-        <v>10.85358927129134</v>
-      </c>
-      <c r="N231" t="n">
-        <v>1.461946661920293</v>
-      </c>
-      <c r="O231" t="n">
-        <v>6.157767966605816</v>
-      </c>
+        <v>13.13596054003147</v>
+      </c>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
       <c r="P231" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q231" t="n">
-        <v>64.63462753818638</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -13997,26 +13685,20 @@
         <v>19</v>
       </c>
       <c r="K232" t="n">
-        <v>2.177717576724394</v>
+        <v>2.178366503501772</v>
       </c>
       <c r="L232" t="n">
         <v>38.29413596121093</v>
       </c>
       <c r="M232" t="n">
-        <v>9.881316214137952</v>
-      </c>
-      <c r="N232" t="n">
-        <v>1.420291070604167</v>
-      </c>
-      <c r="O232" t="n">
-        <v>5.650803642371059</v>
-      </c>
+        <v>13.13596054003147</v>
+      </c>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q232" t="n">
-        <v>61.46180765519166</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -14056,26 +13738,20 @@
         <v>19</v>
       </c>
       <c r="K233" t="n">
-        <v>1.931966466609836</v>
+        <v>1.933592818035819</v>
       </c>
       <c r="L233" t="n">
         <v>38.51892078328299</v>
       </c>
       <c r="M233" t="n">
-        <v>11.14758600080647</v>
-      </c>
-      <c r="N233" t="n">
-        <v>1.32467499222168</v>
-      </c>
-      <c r="O233" t="n">
-        <v>6.236130496514077</v>
-      </c>
+        <v>12.34488939642437</v>
+      </c>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
       <c r="P233" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>69.01978770826264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -14115,26 +13791,20 @@
         <v>19</v>
       </c>
       <c r="K234" t="n">
-        <v>1.931966466609836</v>
+        <v>1.933592818035819</v>
       </c>
       <c r="L234" t="n">
         <v>38.54815454547631</v>
       </c>
       <c r="M234" t="n">
-        <v>11.14758600080647</v>
-      </c>
-      <c r="N234" t="n">
-        <v>1.32467499222168</v>
-      </c>
-      <c r="O234" t="n">
-        <v>6.236130496514077</v>
-      </c>
+        <v>12.34488939642437</v>
+      </c>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q234" t="n">
-        <v>69.01978770826264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -14174,26 +13844,20 @@
         <v>19</v>
       </c>
       <c r="K235" t="n">
-        <v>1.931966466609836</v>
+        <v>1.933592818035819</v>
       </c>
       <c r="L235" t="n">
         <v>38.55657287623865</v>
       </c>
       <c r="M235" t="n">
-        <v>11.14758600080647</v>
-      </c>
-      <c r="N235" t="n">
-        <v>1.32467499222168</v>
-      </c>
-      <c r="O235" t="n">
-        <v>6.236130496514077</v>
-      </c>
+        <v>12.34488939642437</v>
+      </c>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
       <c r="P235" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q235" t="n">
-        <v>69.01978770826264</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -14233,26 +13897,20 @@
         <v>19</v>
       </c>
       <c r="K236" t="n">
-        <v>1.753667849845577</v>
+        <v>1.754995274249072</v>
       </c>
       <c r="L236" t="n">
         <v>38.76513256849518</v>
       </c>
       <c r="M236" t="n">
-        <v>11.26473801004819</v>
-      </c>
-      <c r="N236" t="n">
-        <v>1.293556778531761</v>
-      </c>
-      <c r="O236" t="n">
-        <v>6.279147394289977</v>
-      </c>
+        <v>11.66917292052748</v>
+      </c>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
       <c r="P236" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q236" t="n">
-        <v>72.07156099822888</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -14292,26 +13950,20 @@
         <v>19</v>
       </c>
       <c r="K237" t="n">
-        <v>1.684167938405999</v>
+        <v>1.685429034276147</v>
       </c>
       <c r="L237" t="n">
         <v>38.87734821904463</v>
       </c>
       <c r="M237" t="n">
-        <v>11.26473801004819</v>
-      </c>
-      <c r="N237" t="n">
-        <v>1.277506678189047</v>
-      </c>
-      <c r="O237" t="n">
-        <v>6.27112234411862</v>
-      </c>
+        <v>11.44003729032269</v>
+      </c>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
       <c r="P237" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>73.1440746011677</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -14351,26 +14003,20 @@
         <v>19</v>
       </c>
       <c r="K238" t="n">
-        <v>1.550416454239708</v>
+        <v>1.550940467234431</v>
       </c>
       <c r="L238" t="n">
         <v>39.07896432034089</v>
       </c>
       <c r="M238" t="n">
-        <v>11.9975006749236</v>
-      </c>
-      <c r="N238" t="n">
-        <v>1.277506678189047</v>
-      </c>
-      <c r="O238" t="n">
-        <v>6.637503676556325</v>
-      </c>
+        <v>11.37095695966775</v>
+      </c>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
       <c r="P238" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>76.64157294984587</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -14410,26 +14056,20 @@
         <v>19</v>
       </c>
       <c r="K239" t="n">
-        <v>1.536458559223906</v>
+        <v>1.536523705686497</v>
       </c>
       <c r="L239" t="n">
         <v>39.13578390611895</v>
       </c>
       <c r="M239" t="n">
-        <v>11.9975006749236</v>
-      </c>
-      <c r="N239" t="n">
-        <v>1.31660137030518</v>
-      </c>
-      <c r="O239" t="n">
-        <v>6.657051022614392</v>
-      </c>
+        <v>11.37095695966775</v>
+      </c>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
       <c r="P239" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q239" t="n">
-        <v>76.9198320096321</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -14469,26 +14109,20 @@
         <v>19</v>
       </c>
       <c r="K240" t="n">
-        <v>1.529696341903444</v>
+        <v>1.529883158643096</v>
       </c>
       <c r="L240" t="n">
         <v>39.31505751372828</v>
       </c>
       <c r="M240" t="n">
-        <v>11.9975006749236</v>
-      </c>
-      <c r="N240" t="n">
-        <v>1.383435263799999</v>
-      </c>
-      <c r="O240" t="n">
-        <v>6.690467969361801</v>
-      </c>
+        <v>11.0824964530113</v>
+      </c>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
       <c r="P240" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>77.13618316523589</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -14528,26 +14162,20 @@
         <v>19</v>
       </c>
       <c r="K241" t="n">
-        <v>1.515966964593562</v>
+        <v>1.516284167734536</v>
       </c>
       <c r="L241" t="n">
         <v>39.42637704800809</v>
       </c>
       <c r="M241" t="n">
-        <v>11.9975006749236</v>
-      </c>
-      <c r="N241" t="n">
-        <v>1.383435263799999</v>
-      </c>
-      <c r="O241" t="n">
-        <v>6.690467969361801</v>
-      </c>
+        <v>11.0824964530113</v>
+      </c>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
       <c r="P241" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>77.34139119212958</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -14587,26 +14215,20 @@
         <v>19</v>
       </c>
       <c r="K242" t="n">
-        <v>1.57526681032956</v>
+        <v>1.575369455919398</v>
       </c>
       <c r="L242" t="n">
         <v>39.81079387917911</v>
       </c>
       <c r="M242" t="n">
-        <v>15.04996711991609</v>
-      </c>
-      <c r="N242" t="n">
-        <v>1.498511757301624</v>
-      </c>
-      <c r="O242" t="n">
-        <v>8.274239438608857</v>
-      </c>
+        <v>11.38295853545234</v>
+      </c>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
       <c r="P242" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>80.96179326187823</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -14646,26 +14268,20 @@
         <v>19</v>
       </c>
       <c r="K243" t="n">
-        <v>1.570788183585383</v>
+        <v>1.570954752442219</v>
       </c>
       <c r="L243" t="n">
         <v>39.93511065664422</v>
       </c>
       <c r="M243" t="n">
-        <v>18.76213980838786</v>
-      </c>
-      <c r="N243" t="n">
-        <v>1.498511757301624</v>
-      </c>
-      <c r="O243" t="n">
-        <v>10.13032578284474</v>
-      </c>
+        <v>11.40906398075885</v>
+      </c>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
       <c r="P243" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q243" t="n">
-        <v>84.49419873302156</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -14705,26 +14321,20 @@
         <v>19</v>
       </c>
       <c r="K244" t="n">
-        <v>1.560375385242723</v>
+        <v>1.560583491618936</v>
       </c>
       <c r="L244" t="n">
         <v>40.01996951296049</v>
       </c>
       <c r="M244" t="n">
-        <v>18.76213980838786</v>
-      </c>
-      <c r="N244" t="n">
-        <v>8.887786813876279</v>
-      </c>
-      <c r="O244" t="n">
-        <v>13.82496331113207</v>
-      </c>
+        <v>11.40906398075885</v>
+      </c>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
       <c r="P244" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>88.71334881600528</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -14764,26 +14374,20 @@
         <v>19</v>
       </c>
       <c r="K245" t="n">
-        <v>1.565429483712482</v>
+        <v>1.565210337580271</v>
       </c>
       <c r="L245" t="n">
         <v>40.04664202027453</v>
       </c>
       <c r="M245" t="n">
-        <v>18.76213980838786</v>
-      </c>
-      <c r="N245" t="n">
-        <v>8.887786813876279</v>
-      </c>
-      <c r="O245" t="n">
-        <v>13.82496331113207</v>
-      </c>
+        <v>11.40906398075885</v>
+      </c>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
       <c r="P245" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>88.67679104470409</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -14823,26 +14427,20 @@
         <v>19</v>
       </c>
       <c r="K246" t="n">
-        <v>1.593142183310019</v>
+        <v>1.592462013330594</v>
       </c>
       <c r="L246" t="n">
         <v>40.27589617403697</v>
       </c>
       <c r="M246" t="n">
-        <v>19.80017486787884</v>
-      </c>
-      <c r="N246" t="n">
-        <v>8.887786813876279</v>
-      </c>
-      <c r="O246" t="n">
-        <v>14.34398084087756</v>
-      </c>
+        <v>11.63801176927609</v>
+      </c>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
       <c r="P246" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>88.89330513625706</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -14882,13 +14480,13 @@
         <v>19</v>
       </c>
       <c r="K247" t="n">
-        <v>1.610697573322888</v>
+        <v>1.610738778778021</v>
       </c>
       <c r="L247" t="n">
         <v>40.60633680834452</v>
       </c>
       <c r="M247" t="n">
-        <v>29.51809009266479</v>
+        <v>12.23561229550869</v>
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
@@ -14935,13 +14533,13 @@
         <v>19</v>
       </c>
       <c r="K248" t="n">
-        <v>1.564238403151555</v>
+        <v>1.565395665479873</v>
       </c>
       <c r="L248" t="n">
         <v>40.83199906661575</v>
       </c>
       <c r="M248" t="n">
-        <v>32.70898051855441</v>
+        <v>12.32493800141896</v>
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
@@ -14988,13 +14586,13 @@
         <v>19</v>
       </c>
       <c r="K249" t="n">
-        <v>1.564238403151555</v>
+        <v>1.565395665479873</v>
       </c>
       <c r="L249" t="n">
         <v>40.83773247919481</v>
       </c>
       <c r="M249" t="n">
-        <v>32.70898051855441</v>
+        <v>12.32493800141896</v>
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
@@ -15041,13 +14639,13 @@
         <v>19</v>
       </c>
       <c r="K250" t="n">
-        <v>1.419537418518715</v>
+        <v>1.419913546667344</v>
       </c>
       <c r="L250" t="n">
         <v>41.24635608576865</v>
       </c>
       <c r="M250" t="n">
-        <v>28.60411152728559</v>
+        <v>13.10942074896131</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
@@ -15094,13 +14692,13 @@
         <v>19</v>
       </c>
       <c r="K251" t="n">
-        <v>1.418578208833067</v>
+        <v>1.418340009755992</v>
       </c>
       <c r="L251" t="n">
         <v>41.33632190899264</v>
       </c>
       <c r="M251" t="n">
-        <v>28.60411152728559</v>
+        <v>13.21905420441579</v>
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
@@ -15147,13 +14745,13 @@
         <v>19</v>
       </c>
       <c r="K252" t="n">
-        <v>1.431146441684962</v>
+        <v>1.430984911351356</v>
       </c>
       <c r="L252" t="n">
         <v>41.45587863535442</v>
       </c>
       <c r="M252" t="n">
-        <v>28.60411152728559</v>
+        <v>13.41609389853743</v>
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
@@ -15200,13 +14798,13 @@
         <v>19</v>
       </c>
       <c r="K253" t="n">
-        <v>1.403846864611153</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="L253" t="n">
         <v>41.86799420558921</v>
       </c>
       <c r="M253" t="n">
-        <v>3.785458746171327</v>
+        <v>13.90173162460115</v>
       </c>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
@@ -15253,13 +14851,13 @@
         <v>19</v>
       </c>
       <c r="K254" t="n">
-        <v>1.403846864611153</v>
+        <v>1.404009728377235</v>
       </c>
       <c r="L254" t="n">
         <v>41.9343848009507</v>
       </c>
       <c r="M254" t="n">
-        <v>3.785458746171327</v>
+        <v>13.90173162460115</v>
       </c>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
@@ -15306,13 +14904,13 @@
         <v>19</v>
       </c>
       <c r="K255" t="n">
-        <v>1.391102713591947</v>
+        <v>1.391576045106675</v>
       </c>
       <c r="L255" t="n">
         <v>41.97728717868476</v>
       </c>
       <c r="M255" t="n">
-        <v>3.785458746171327</v>
+        <v>13.90173162460115</v>
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
@@ -15359,13 +14957,13 @@
         <v>19</v>
       </c>
       <c r="K256" t="n">
-        <v>1.371697587884001</v>
+        <v>1.372309295002918</v>
       </c>
       <c r="L256" t="n">
         <v>42.1080780001725</v>
       </c>
       <c r="M256" t="n">
-        <v>3.785458746171327</v>
+        <v>13.08958004473499</v>
       </c>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
@@ -15412,13 +15010,13 @@
         <v>19</v>
       </c>
       <c r="K257" t="n">
-        <v>1.367004314028125</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="L257" t="n">
         <v>42.36064170397581</v>
       </c>
       <c r="M257" t="n">
-        <v>2.304981288314705</v>
+        <v>12.78976864218879</v>
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
@@ -15465,13 +15063,13 @@
         <v>19</v>
       </c>
       <c r="K258" t="n">
-        <v>1.367004314028125</v>
+        <v>1.368185694053874</v>
       </c>
       <c r="L258" t="n">
         <v>42.36544121775962</v>
       </c>
       <c r="M258" t="n">
-        <v>2.304981288314705</v>
+        <v>12.78976864218879</v>
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
@@ -15518,13 +15116,13 @@
         <v>19</v>
       </c>
       <c r="K259" t="n">
-        <v>1.473969960651437</v>
+        <v>1.474906345155731</v>
       </c>
       <c r="L259" t="n">
         <v>42.62910541347231</v>
       </c>
       <c r="M259" t="n">
-        <v>2.304981288314705</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
@@ -15571,13 +15169,13 @@
         <v>19</v>
       </c>
       <c r="K260" t="n">
-        <v>1.473969960651437</v>
+        <v>1.474906345155731</v>
       </c>
       <c r="L260" t="n">
         <v>42.65749478829041</v>
       </c>
       <c r="M260" t="n">
-        <v>2.304981288314705</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="N260" t="inlineStr"/>
       <c r="O260" t="inlineStr"/>
@@ -15624,13 +15222,13 @@
         <v>19</v>
       </c>
       <c r="K261" t="n">
-        <v>1.473969960651437</v>
+        <v>1.474906345155731</v>
       </c>
       <c r="L261" t="n">
         <v>42.65761991966455</v>
       </c>
       <c r="M261" t="n">
-        <v>2.304981288314705</v>
+        <v>12.02344956757194</v>
       </c>
       <c r="N261" t="inlineStr"/>
       <c r="O261" t="inlineStr"/>
@@ -15677,13 +15275,13 @@
         <v>19</v>
       </c>
       <c r="K262" t="n">
-        <v>1.452318781636996</v>
+        <v>1.452702989955006</v>
       </c>
       <c r="L262" t="n">
         <v>42.9514979765695</v>
       </c>
       <c r="M262" t="n">
-        <v>2.208926235719771</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="N262" t="inlineStr"/>
       <c r="O262" t="inlineStr"/>
@@ -15730,13 +15328,13 @@
         <v>19</v>
       </c>
       <c r="K263" t="n">
-        <v>1.452318781636996</v>
+        <v>1.452702989955006</v>
       </c>
       <c r="L263" t="n">
         <v>42.96494800841049</v>
       </c>
       <c r="M263" t="n">
-        <v>2.208926235719771</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
@@ -15783,13 +15381,13 @@
         <v>19</v>
       </c>
       <c r="K264" t="n">
-        <v>1.452318781636996</v>
+        <v>1.452702989955006</v>
       </c>
       <c r="L264" t="n">
         <v>42.96499918794486</v>
       </c>
       <c r="M264" t="n">
-        <v>2.208926235719771</v>
+        <v>11.35486375876084</v>
       </c>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
@@ -15836,13 +15434,13 @@
         <v>19</v>
       </c>
       <c r="K265" t="n">
-        <v>1.455108032295628</v>
+        <v>1.449384850451923</v>
       </c>
       <c r="L265" t="n">
         <v>43.04887327599852</v>
       </c>
       <c r="M265" t="n">
-        <v>2.208926235719771</v>
+        <v>10.84914955146178</v>
       </c>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
@@ -15889,13 +15487,13 @@
         <v>19</v>
       </c>
       <c r="K266" t="n">
-        <v>1.455108032295628</v>
+        <v>1.449384850451923</v>
       </c>
       <c r="L266" t="n">
         <v>43.0730033382665</v>
       </c>
       <c r="M266" t="n">
-        <v>2.208926235719771</v>
+        <v>10.84914955146178</v>
       </c>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
@@ -15942,13 +15540,13 @@
         <v>19</v>
       </c>
       <c r="K267" t="n">
-        <v>1.461946661920293</v>
+        <v>1.45809868005846</v>
       </c>
       <c r="L267" t="n">
         <v>43.13696400318495</v>
       </c>
       <c r="M267" t="n">
-        <v>2.208926235719771</v>
+        <v>10.84914955146178</v>
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
@@ -15995,13 +15593,13 @@
         <v>19</v>
       </c>
       <c r="K268" t="n">
-        <v>1.420291070604167</v>
+        <v>1.420974824777689</v>
       </c>
       <c r="L268" t="n">
         <v>43.40717842679832</v>
       </c>
       <c r="M268" t="n">
-        <v>1.931966466609836</v>
+        <v>9.795415074047549</v>
       </c>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
@@ -16048,13 +15646,13 @@
         <v>19</v>
       </c>
       <c r="K269" t="n">
-        <v>1.420291070604167</v>
+        <v>1.420974824777689</v>
       </c>
       <c r="L269" t="n">
         <v>43.41052606219485</v>
       </c>
       <c r="M269" t="n">
-        <v>1.931966466609836</v>
+        <v>9.795415074047549</v>
       </c>
       <c r="N269" t="inlineStr"/>
       <c r="O269" t="inlineStr"/>
@@ -16101,13 +15699,13 @@
         <v>19</v>
       </c>
       <c r="K270" t="n">
-        <v>1.32467499222168</v>
+        <v>1.324786460954448</v>
       </c>
       <c r="L270" t="n">
         <v>43.59231633847489</v>
       </c>
       <c r="M270" t="n">
-        <v>1.931966466609836</v>
+        <v>11.14361891424003</v>
       </c>
       <c r="N270" t="inlineStr"/>
       <c r="O270" t="inlineStr"/>
@@ -16154,13 +15752,13 @@
         <v>19</v>
       </c>
       <c r="K271" t="n">
-        <v>1.32467499222168</v>
+        <v>1.324786460954448</v>
       </c>
       <c r="L271" t="n">
         <v>43.59377323323952</v>
       </c>
       <c r="M271" t="n">
-        <v>1.931966466609836</v>
+        <v>11.14361891424003</v>
       </c>
       <c r="N271" t="inlineStr"/>
       <c r="O271" t="inlineStr"/>
@@ -16207,13 +15805,13 @@
         <v>19</v>
       </c>
       <c r="K272" t="n">
-        <v>1.293556778531761</v>
+        <v>1.292365108441281</v>
       </c>
       <c r="L272" t="n">
         <v>43.68927611556463</v>
       </c>
       <c r="M272" t="n">
-        <v>1.753667849845577</v>
+        <v>11.2617197355591</v>
       </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
@@ -16260,13 +15858,13 @@
         <v>19</v>
       </c>
       <c r="K273" t="n">
-        <v>1.293556778531761</v>
+        <v>1.292365108441281</v>
       </c>
       <c r="L273" t="n">
         <v>43.69044460908282</v>
       </c>
       <c r="M273" t="n">
-        <v>1.753667849845577</v>
+        <v>11.2617197355591</v>
       </c>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
@@ -16313,13 +15911,13 @@
         <v>19</v>
       </c>
       <c r="K274" t="n">
-        <v>1.277506678189047</v>
+        <v>1.277746647343163</v>
       </c>
       <c r="L274" t="n">
         <v>44.00818123826782</v>
       </c>
       <c r="M274" t="n">
-        <v>1.550416454239708</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
@@ -16366,13 +15964,13 @@
         <v>19</v>
       </c>
       <c r="K275" t="n">
-        <v>1.277506678189047</v>
+        <v>1.277746647343163</v>
       </c>
       <c r="L275" t="n">
         <v>44.06893143710035</v>
       </c>
       <c r="M275" t="n">
-        <v>1.550416454239708</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
@@ -16419,13 +16017,13 @@
         <v>19</v>
       </c>
       <c r="K276" t="n">
-        <v>1.31660137030518</v>
+        <v>1.314231504832959</v>
       </c>
       <c r="L276" t="n">
         <v>44.12573234292111</v>
       </c>
       <c r="M276" t="n">
-        <v>1.536458559223906</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
@@ -16472,13 +16070,13 @@
         <v>19</v>
       </c>
       <c r="K277" t="n">
-        <v>1.31660137030518</v>
+        <v>1.314231504832959</v>
       </c>
       <c r="L277" t="n">
         <v>44.12641920032384</v>
       </c>
       <c r="M277" t="n">
-        <v>1.536458559223906</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
@@ -16525,13 +16123,13 @@
         <v>19</v>
       </c>
       <c r="K278" t="n">
-        <v>1.383435263799999</v>
+        <v>1.383519409319435</v>
       </c>
       <c r="L278" t="n">
         <v>44.34632336957541</v>
       </c>
       <c r="M278" t="n">
-        <v>1.529696341903444</v>
+        <v>11.99573651073132</v>
       </c>
       <c r="N278" t="inlineStr"/>
       <c r="O278" t="inlineStr"/>
@@ -16578,13 +16176,13 @@
         <v>19</v>
       </c>
       <c r="K279" t="n">
-        <v>1.466321471857125</v>
+        <v>1.464483325120127</v>
       </c>
       <c r="L279" t="n">
         <v>44.59891462884396</v>
       </c>
       <c r="M279" t="n">
-        <v>1.515966964593562</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="N279" t="inlineStr"/>
       <c r="O279" t="inlineStr"/>
@@ -16631,13 +16229,13 @@
         <v>19</v>
       </c>
       <c r="K280" t="n">
-        <v>1.498511757301624</v>
+        <v>1.494545066258282</v>
       </c>
       <c r="L280" t="n">
         <v>44.64041315209489</v>
       </c>
       <c r="M280" t="n">
-        <v>1.57526681032956</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="N280" t="inlineStr"/>
       <c r="O280" t="inlineStr"/>
@@ -16684,13 +16282,13 @@
         <v>19</v>
       </c>
       <c r="K281" t="n">
-        <v>1.498511757301624</v>
+        <v>1.494545066258282</v>
       </c>
       <c r="L281" t="n">
         <v>44.66154577756325</v>
       </c>
       <c r="M281" t="n">
-        <v>1.57526681032956</v>
+        <v>15.04459428310597</v>
       </c>
       <c r="N281" t="inlineStr"/>
       <c r="O281" t="inlineStr"/>
@@ -16737,13 +16335,13 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>8.887786813876279</v>
+        <v>8.876632772914137</v>
       </c>
       <c r="L282" t="n">
         <v>45.30828076852884</v>
       </c>
       <c r="M282" t="n">
-        <v>1.593142183310019</v>
+        <v>19.78860372735059</v>
       </c>
       <c r="N282" t="inlineStr"/>
       <c r="O282" t="inlineStr"/>
